--- a/research/traditional_assets/database/data/kuwait/kuwait_education.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_education.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08542848526327119</v>
+        <v>0.08533859253537629</v>
       </c>
       <c r="C2">
-        <v>1185.365605451076</v>
+        <v>1174.329301764484</v>
       </c>
       <c r="D2">
-        <v>953.5656054510758</v>
+        <v>954.3832017644844</v>
       </c>
       <c r="E2">
-        <v>-1.79</v>
+        <v>10.0639</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.8539</v>
       </c>
       <c r="G2">
         <v>231.8</v>
@@ -1451,28 +1451,28 @@
         <v>126.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5962511699999999</v>
       </c>
       <c r="N2">
-        <v>126.8</v>
+        <v>126.20374883</v>
       </c>
       <c r="O2">
-        <v>19.02</v>
+        <v>18.9305623245</v>
       </c>
       <c r="P2">
-        <v>107.78</v>
+        <v>107.2731865055</v>
       </c>
       <c r="Q2">
-        <v>118.68</v>
+        <v>118.1731865055</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08542848526327119</v>
+        <v>0.08576872983371342</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7581920355861339</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>212.6620564954196</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08533859253537629</v>
+        <v>0.08524869980748138</v>
       </c>
       <c r="C3">
-        <v>1174.329301764484</v>
+        <v>1163.29440131091</v>
       </c>
       <c r="D3">
-        <v>954.3832017644844</v>
+        <v>955.20220131091</v>
       </c>
       <c r="E3">
-        <v>10.0639</v>
+        <v>21.9178</v>
       </c>
       <c r="F3">
-        <v>11.8539</v>
+        <v>23.7078</v>
       </c>
       <c r="G3">
         <v>231.8</v>
@@ -1533,28 +1533,28 @@
         <v>126.8</v>
       </c>
       <c r="M3">
-        <v>0.5962511699999999</v>
+        <v>1.19250234</v>
       </c>
       <c r="N3">
-        <v>126.20374883</v>
+        <v>125.60749766</v>
       </c>
       <c r="O3">
-        <v>18.9305623245</v>
+        <v>18.841124649</v>
       </c>
       <c r="P3">
-        <v>107.2731865055</v>
+        <v>106.766373011</v>
       </c>
       <c r="Q3">
-        <v>118.1731865055</v>
+        <v>117.666373011</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08576872983371342</v>
+        <v>0.08611591817089938</v>
       </c>
       <c r="T3">
-        <v>0.7581920355861339</v>
+        <v>0.7647780700485237</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>212.6620564954196</v>
+        <v>106.3310282477098</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08524869980748138</v>
+        <v>0.08515880707958647</v>
       </c>
       <c r="C4">
-        <v>1163.29440131091</v>
+        <v>1152.26090770599</v>
       </c>
       <c r="D4">
-        <v>955.20220131091</v>
+        <v>956.0226077059896</v>
       </c>
       <c r="E4">
-        <v>21.9178</v>
+        <v>33.7717</v>
       </c>
       <c r="F4">
-        <v>23.7078</v>
+        <v>35.56169999999999</v>
       </c>
       <c r="G4">
         <v>231.8</v>
@@ -1615,28 +1615,28 @@
         <v>126.8</v>
       </c>
       <c r="M4">
-        <v>1.19250234</v>
+        <v>1.78875351</v>
       </c>
       <c r="N4">
-        <v>125.60749766</v>
+        <v>125.01124649</v>
       </c>
       <c r="O4">
-        <v>18.841124649</v>
+        <v>18.7516869735</v>
       </c>
       <c r="P4">
-        <v>106.766373011</v>
+        <v>106.2595595165</v>
       </c>
       <c r="Q4">
-        <v>117.666373011</v>
+        <v>117.1595595165</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08611591817089938</v>
+        <v>0.08647026503050152</v>
       </c>
       <c r="T4">
-        <v>0.7647780700485237</v>
+        <v>0.771499899035911</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.3310282477098</v>
+        <v>70.88735216513986</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08515880707958647</v>
+        <v>0.08506891435169156</v>
       </c>
       <c r="C5">
-        <v>1152.26090770599</v>
+        <v>1141.228824577792</v>
       </c>
       <c r="D5">
-        <v>956.0226077059896</v>
+        <v>956.8444245777915</v>
       </c>
       <c r="E5">
-        <v>33.7717</v>
+        <v>45.6256</v>
       </c>
       <c r="F5">
-        <v>35.56169999999999</v>
+        <v>47.4156</v>
       </c>
       <c r="G5">
         <v>231.8</v>
@@ -1697,28 +1697,28 @@
         <v>126.8</v>
       </c>
       <c r="M5">
-        <v>1.78875351</v>
+        <v>2.38500468</v>
       </c>
       <c r="N5">
-        <v>125.01124649</v>
+        <v>124.41499532</v>
       </c>
       <c r="O5">
-        <v>18.7516869735</v>
+        <v>18.662249298</v>
       </c>
       <c r="P5">
-        <v>106.2595595165</v>
+        <v>105.752746022</v>
       </c>
       <c r="Q5">
-        <v>117.1595595165</v>
+        <v>116.652746022</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08647026503050152</v>
+        <v>0.08683199411634539</v>
       </c>
       <c r="T5">
-        <v>0.771499899035911</v>
+        <v>0.7783617661272023</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.88735216513986</v>
+        <v>53.16551412385489</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08506891435169156</v>
+        <v>0.08497902162379666</v>
       </c>
       <c r="C6">
-        <v>1141.228824577792</v>
+        <v>1130.198155566871</v>
       </c>
       <c r="D6">
-        <v>956.8444245777915</v>
+        <v>957.6676555668708</v>
       </c>
       <c r="E6">
-        <v>45.6256</v>
+        <v>57.47949999999999</v>
       </c>
       <c r="F6">
-        <v>47.4156</v>
+        <v>59.26949999999999</v>
       </c>
       <c r="G6">
         <v>231.8</v>
@@ -1779,28 +1779,28 @@
         <v>126.8</v>
       </c>
       <c r="M6">
-        <v>2.38500468</v>
+        <v>2.98125585</v>
       </c>
       <c r="N6">
-        <v>124.41499532</v>
+        <v>123.81874415</v>
       </c>
       <c r="O6">
-        <v>18.662249298</v>
+        <v>18.5728116225</v>
       </c>
       <c r="P6">
-        <v>105.752746022</v>
+        <v>105.2459325275</v>
       </c>
       <c r="Q6">
-        <v>116.652746022</v>
+        <v>116.1459325275</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08683199411634539</v>
+        <v>0.08720133855136492</v>
       </c>
       <c r="T6">
-        <v>0.7783617661272023</v>
+        <v>0.7853680935783103</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.16551412385489</v>
+        <v>42.53241129908391</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08497902162379666</v>
+        <v>0.08488912889590176</v>
       </c>
       <c r="C7">
-        <v>1130.198155566871</v>
+        <v>1119.168904326321</v>
       </c>
       <c r="D7">
-        <v>957.6676555668708</v>
+        <v>958.4923043263211</v>
       </c>
       <c r="E7">
-        <v>57.47949999999999</v>
+        <v>69.3334</v>
       </c>
       <c r="F7">
-        <v>59.26949999999999</v>
+        <v>71.1234</v>
       </c>
       <c r="G7">
         <v>231.8</v>
@@ -1861,28 +1861,28 @@
         <v>126.8</v>
       </c>
       <c r="M7">
-        <v>2.98125585</v>
+        <v>3.57750702</v>
       </c>
       <c r="N7">
-        <v>123.81874415</v>
+        <v>123.22249298</v>
       </c>
       <c r="O7">
-        <v>18.5728116225</v>
+        <v>18.483373947</v>
       </c>
       <c r="P7">
-        <v>105.2459325275</v>
+        <v>104.739119033</v>
       </c>
       <c r="Q7">
-        <v>116.1459325275</v>
+        <v>115.639119033</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08720133855136492</v>
+        <v>0.0875785413786189</v>
       </c>
       <c r="T7">
-        <v>0.7853680935783103</v>
+        <v>0.7925234918262501</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.53241129908391</v>
+        <v>35.44367608256992</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08488912889590175</v>
+        <v>0.08479923616800687</v>
       </c>
       <c r="C8">
-        <v>1119.168904326321</v>
+        <v>1108.141074521831</v>
       </c>
       <c r="D8">
-        <v>958.4923043263213</v>
+        <v>959.3183745218311</v>
       </c>
       <c r="E8">
-        <v>69.33339999999998</v>
+        <v>81.18729999999998</v>
       </c>
       <c r="F8">
-        <v>71.12339999999999</v>
+        <v>82.97729999999999</v>
       </c>
       <c r="G8">
         <v>231.8</v>
@@ -1943,28 +1943,28 @@
         <v>126.8</v>
       </c>
       <c r="M8">
-        <v>3.577507019999999</v>
+        <v>4.173758189999999</v>
       </c>
       <c r="N8">
-        <v>123.22249298</v>
+        <v>122.62624181</v>
       </c>
       <c r="O8">
-        <v>18.483373947</v>
+        <v>18.3939362715</v>
       </c>
       <c r="P8">
-        <v>104.739119033</v>
+        <v>104.2323055385</v>
       </c>
       <c r="Q8">
-        <v>115.639119033</v>
+        <v>115.1323055385</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0875785413786189</v>
+        <v>0.08796385609463103</v>
       </c>
       <c r="T8">
-        <v>0.7925234918262501</v>
+        <v>0.799832769606404</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.44367608256993</v>
+        <v>30.38029378505994</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08479923616800686</v>
+        <v>0.08470934344011195</v>
       </c>
       <c r="C9">
-        <v>1108.141074521831</v>
+        <v>1097.114669831736</v>
       </c>
       <c r="D9">
-        <v>959.3183745218311</v>
+        <v>960.145869831736</v>
       </c>
       <c r="E9">
-        <v>81.18729999999999</v>
+        <v>93.04119999999999</v>
       </c>
       <c r="F9">
-        <v>82.9773</v>
+        <v>94.8312</v>
       </c>
       <c r="G9">
         <v>231.8</v>
@@ -2025,28 +2025,28 @@
         <v>126.8</v>
       </c>
       <c r="M9">
-        <v>4.17375819</v>
+        <v>4.77000936</v>
       </c>
       <c r="N9">
-        <v>122.62624181</v>
+        <v>122.02999064</v>
       </c>
       <c r="O9">
-        <v>18.3939362715</v>
+        <v>18.304498596</v>
       </c>
       <c r="P9">
-        <v>104.2323055385</v>
+        <v>103.725492044</v>
       </c>
       <c r="Q9">
-        <v>115.1323055385</v>
+        <v>114.625492044</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08796385609463103</v>
+        <v>0.08835754721751299</v>
       </c>
       <c r="T9">
-        <v>0.799832769606404</v>
+        <v>0.8073009447296047</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.38029378505993</v>
+        <v>26.58275706192745</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08470934344011195</v>
+        <v>0.08461945071221703</v>
       </c>
       <c r="C10">
-        <v>1097.114669831736</v>
+        <v>1086.089693947074</v>
       </c>
       <c r="D10">
-        <v>960.145869831736</v>
+        <v>960.9747939470741</v>
       </c>
       <c r="E10">
-        <v>93.04119999999999</v>
+        <v>104.8951</v>
       </c>
       <c r="F10">
-        <v>94.8312</v>
+        <v>106.6851</v>
       </c>
       <c r="G10">
         <v>231.8</v>
@@ -2107,28 +2107,28 @@
         <v>126.8</v>
       </c>
       <c r="M10">
-        <v>4.77000936</v>
+        <v>5.366260529999999</v>
       </c>
       <c r="N10">
-        <v>122.02999064</v>
+        <v>121.43373947</v>
       </c>
       <c r="O10">
-        <v>18.304498596</v>
+        <v>18.2150609205</v>
       </c>
       <c r="P10">
-        <v>103.725492044</v>
+        <v>103.2186785495</v>
       </c>
       <c r="Q10">
-        <v>114.625492044</v>
+        <v>114.1186785495</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08835754721751299</v>
+        <v>0.08875989089254618</v>
       </c>
       <c r="T10">
-        <v>0.8073009447296047</v>
+        <v>0.8149332555697986</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.58275706192745</v>
+        <v>23.62911738837995</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08461945071221703</v>
+        <v>0.08452955798432214</v>
       </c>
       <c r="C11">
-        <v>1086.089693947074</v>
+        <v>1075.066150571641</v>
       </c>
       <c r="D11">
-        <v>960.9747939470741</v>
+        <v>961.8051505716406</v>
       </c>
       <c r="E11">
-        <v>104.8951</v>
+        <v>116.749</v>
       </c>
       <c r="F11">
-        <v>106.6851</v>
+        <v>118.539</v>
       </c>
       <c r="G11">
         <v>231.8</v>
@@ -2189,28 +2189,28 @@
         <v>126.8</v>
       </c>
       <c r="M11">
-        <v>5.366260529999999</v>
+        <v>5.962511699999999</v>
       </c>
       <c r="N11">
-        <v>121.43373947</v>
+        <v>120.8374883</v>
       </c>
       <c r="O11">
-        <v>18.2150609205</v>
+        <v>18.125623245</v>
       </c>
       <c r="P11">
-        <v>103.2186785495</v>
+        <v>102.711865055</v>
       </c>
       <c r="Q11">
-        <v>114.1186785495</v>
+        <v>113.611865055</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08875989089254618</v>
+        <v>0.08917117553813571</v>
       </c>
       <c r="T11">
-        <v>0.8149332555697986</v>
+        <v>0.8227351733175526</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.62911738837995</v>
+        <v>21.26620564954196</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08452955798432214</v>
+        <v>0.08443966525642722</v>
       </c>
       <c r="C12">
-        <v>1075.066150571641</v>
+        <v>1064.044043422044</v>
       </c>
       <c r="D12">
-        <v>961.8051505716406</v>
+        <v>962.6369434220442</v>
       </c>
       <c r="E12">
-        <v>116.749</v>
+        <v>128.6029</v>
       </c>
       <c r="F12">
-        <v>118.539</v>
+        <v>130.3929</v>
       </c>
       <c r="G12">
         <v>231.8</v>
@@ -2271,28 +2271,28 @@
         <v>126.8</v>
       </c>
       <c r="M12">
-        <v>5.962511699999999</v>
+        <v>6.55876287</v>
       </c>
       <c r="N12">
-        <v>120.8374883</v>
+        <v>120.24123713</v>
       </c>
       <c r="O12">
-        <v>18.125623245</v>
+        <v>18.0361855695</v>
       </c>
       <c r="P12">
-        <v>102.711865055</v>
+        <v>102.2050515605</v>
       </c>
       <c r="Q12">
-        <v>113.611865055</v>
+        <v>113.1050515605</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08917117553813571</v>
+        <v>0.08959170253531148</v>
       </c>
       <c r="T12">
-        <v>0.8227351733175526</v>
+        <v>0.830712415059638</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.26620564954196</v>
+        <v>19.33291422685632</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08443966525642722</v>
+        <v>0.0843497725285323</v>
       </c>
       <c r="C13">
-        <v>1064.044043422044</v>
+        <v>1053.023376227761</v>
       </c>
       <c r="D13">
-        <v>962.6369434220442</v>
+        <v>963.4701762277606</v>
       </c>
       <c r="E13">
-        <v>128.6029</v>
+        <v>140.4568</v>
       </c>
       <c r="F13">
-        <v>130.3929</v>
+        <v>142.2468</v>
       </c>
       <c r="G13">
         <v>231.8</v>
@@ -2353,28 +2353,28 @@
         <v>126.8</v>
       </c>
       <c r="M13">
-        <v>6.55876287</v>
+        <v>7.155014039999998</v>
       </c>
       <c r="N13">
-        <v>120.24123713</v>
+        <v>119.64498596</v>
       </c>
       <c r="O13">
-        <v>18.0361855695</v>
+        <v>17.946747894</v>
       </c>
       <c r="P13">
-        <v>102.2050515605</v>
+        <v>101.698238066</v>
       </c>
       <c r="Q13">
-        <v>113.1050515605</v>
+        <v>112.598238066</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08959170253531148</v>
+        <v>0.09002178696424126</v>
       </c>
       <c r="T13">
-        <v>0.830712415059638</v>
+        <v>0.8388709577504072</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.33291422685632</v>
+        <v>17.72183804128496</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0843497725285323</v>
+        <v>0.0842598798006374</v>
       </c>
       <c r="C14">
-        <v>1053.023376227761</v>
+        <v>1042.00415273119</v>
       </c>
       <c r="D14">
-        <v>963.4701762277606</v>
+        <v>964.3048527311897</v>
       </c>
       <c r="E14">
-        <v>140.4568</v>
+        <v>152.3107</v>
       </c>
       <c r="F14">
-        <v>142.2468</v>
+        <v>154.1007</v>
       </c>
       <c r="G14">
         <v>231.8</v>
@@ -2435,28 +2435,28 @@
         <v>126.8</v>
       </c>
       <c r="M14">
-        <v>7.155014039999998</v>
+        <v>7.751265209999999</v>
       </c>
       <c r="N14">
-        <v>119.64498596</v>
+        <v>119.04873479</v>
       </c>
       <c r="O14">
-        <v>17.946747894</v>
+        <v>17.8573102185</v>
       </c>
       <c r="P14">
-        <v>101.698238066</v>
+        <v>101.1914245715</v>
       </c>
       <c r="Q14">
-        <v>112.598238066</v>
+        <v>112.0914245715</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09002178696424126</v>
+        <v>0.09046175839153725</v>
       </c>
       <c r="T14">
-        <v>0.8388709577504072</v>
+        <v>0.8472170531467113</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.72183804128496</v>
+        <v>16.35861973041689</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0842598798006374</v>
+        <v>0.08416998707274249</v>
       </c>
       <c r="C15">
-        <v>1042.00415273119</v>
+        <v>1030.986376687711</v>
       </c>
       <c r="D15">
-        <v>964.3048527311897</v>
+        <v>965.1409766877107</v>
       </c>
       <c r="E15">
-        <v>152.3107</v>
+        <v>164.1646</v>
       </c>
       <c r="F15">
-        <v>154.1007</v>
+        <v>165.9546</v>
       </c>
       <c r="G15">
         <v>231.8</v>
@@ -2517,28 +2517,28 @@
         <v>126.8</v>
       </c>
       <c r="M15">
-        <v>7.751265209999999</v>
+        <v>8.34751638</v>
       </c>
       <c r="N15">
-        <v>119.04873479</v>
+        <v>118.45248362</v>
       </c>
       <c r="O15">
-        <v>17.8573102185</v>
+        <v>17.767872543</v>
       </c>
       <c r="P15">
-        <v>101.1914245715</v>
+        <v>100.684611077</v>
       </c>
       <c r="Q15">
-        <v>112.0914245715</v>
+        <v>111.584611077</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09046175839153725</v>
+        <v>0.09091196171249127</v>
       </c>
       <c r="T15">
-        <v>0.8472170531467113</v>
+        <v>0.8557572437847898</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.35861973041689</v>
+        <v>15.19014689252997</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08416998707274249</v>
+        <v>0.08408009434484759</v>
       </c>
       <c r="C16">
-        <v>1030.986376687711</v>
+        <v>1019.97005186574</v>
       </c>
       <c r="D16">
-        <v>965.1409766877107</v>
+        <v>965.9785518657399</v>
       </c>
       <c r="E16">
-        <v>164.1646</v>
+        <v>176.0185</v>
       </c>
       <c r="F16">
-        <v>165.9546</v>
+        <v>177.8085</v>
       </c>
       <c r="G16">
         <v>231.8</v>
@@ -2599,28 +2599,28 @@
         <v>126.8</v>
       </c>
       <c r="M16">
-        <v>8.34751638</v>
+        <v>8.94376755</v>
       </c>
       <c r="N16">
-        <v>118.45248362</v>
+        <v>117.85623245</v>
       </c>
       <c r="O16">
-        <v>17.767872543</v>
+        <v>17.6784348675</v>
       </c>
       <c r="P16">
-        <v>100.684611077</v>
+        <v>100.1777975825</v>
       </c>
       <c r="Q16">
-        <v>111.584611077</v>
+        <v>111.0777975825</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09091196171249127</v>
+        <v>0.09137275805276188</v>
       </c>
       <c r="T16">
-        <v>0.8557572437847898</v>
+        <v>0.8644983800849408</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.19014689252997</v>
+        <v>14.17747043302797</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08408009434484759</v>
+        <v>0.08399020161695268</v>
       </c>
       <c r="C17">
-        <v>1019.97005186574</v>
+        <v>1008.955182046785</v>
       </c>
       <c r="D17">
-        <v>965.9785518657399</v>
+        <v>966.8175820467851</v>
       </c>
       <c r="E17">
-        <v>176.0185</v>
+        <v>187.8724</v>
       </c>
       <c r="F17">
-        <v>177.8085</v>
+        <v>189.6624</v>
       </c>
       <c r="G17">
         <v>231.8</v>
@@ -2681,28 +2681,28 @@
         <v>126.8</v>
       </c>
       <c r="M17">
-        <v>8.943767549999999</v>
+        <v>9.540018719999999</v>
       </c>
       <c r="N17">
-        <v>117.85623245</v>
+        <v>117.25998128</v>
       </c>
       <c r="O17">
-        <v>17.6784348675</v>
+        <v>17.588997192</v>
       </c>
       <c r="P17">
-        <v>100.1777975825</v>
+        <v>99.67098408800001</v>
       </c>
       <c r="Q17">
-        <v>111.0777975825</v>
+        <v>110.570984088</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09137275805276188</v>
+        <v>0.0918445257344675</v>
       </c>
       <c r="T17">
-        <v>0.8644983800849408</v>
+        <v>0.8734476386779528</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.17747043302797</v>
+        <v>13.29137853096372</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08399020161695268</v>
+        <v>0.08411705888905777</v>
       </c>
       <c r="C18">
-        <v>1008.955182046785</v>
+        <v>995.9176589302249</v>
       </c>
       <c r="D18">
-        <v>966.8175820467851</v>
+        <v>965.6339589302248</v>
       </c>
       <c r="E18">
-        <v>187.8724</v>
+        <v>199.7263</v>
       </c>
       <c r="F18">
-        <v>189.6624</v>
+        <v>201.5163</v>
       </c>
       <c r="G18">
         <v>231.8</v>
@@ -2763,45 +2763,45 @@
         <v>126.8</v>
       </c>
       <c r="M18">
-        <v>9.540018719999999</v>
+        <v>10.43854434</v>
       </c>
       <c r="N18">
-        <v>117.25998128</v>
+        <v>116.36145566</v>
       </c>
       <c r="O18">
-        <v>17.588997192</v>
+        <v>17.454218349</v>
       </c>
       <c r="P18">
-        <v>99.67098408800001</v>
+        <v>98.90723731099999</v>
       </c>
       <c r="Q18">
-        <v>110.570984088</v>
+        <v>109.807237311</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0918445257344675</v>
+        <v>0.09232766131211781</v>
       </c>
       <c r="T18">
-        <v>0.8734476386779528</v>
+        <v>0.8826125420563383</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.15</v>
       </c>
       <c r="W18">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.29137853096372</v>
+        <v>12.14728757860505</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08411705888905777</v>
+        <v>0.08403991616116287</v>
       </c>
       <c r="C19">
-        <v>995.9176589302249</v>
+        <v>984.7831822211897</v>
       </c>
       <c r="D19">
-        <v>965.6339589302248</v>
+        <v>966.3533822211898</v>
       </c>
       <c r="E19">
-        <v>199.7263</v>
+        <v>211.5802</v>
       </c>
       <c r="F19">
-        <v>201.5163</v>
+        <v>213.3702</v>
       </c>
       <c r="G19">
         <v>231.8</v>
@@ -2845,28 +2845,28 @@
         <v>126.8</v>
       </c>
       <c r="M19">
-        <v>10.43854434</v>
+        <v>11.05257636</v>
       </c>
       <c r="N19">
-        <v>116.36145566</v>
+        <v>115.74742364</v>
       </c>
       <c r="O19">
-        <v>17.454218349</v>
+        <v>17.362113546</v>
       </c>
       <c r="P19">
-        <v>98.90723731099999</v>
+        <v>98.38531009399999</v>
       </c>
       <c r="Q19">
-        <v>109.807237311</v>
+        <v>109.285310094</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09232766131211781</v>
+        <v>0.09282258068434497</v>
       </c>
       <c r="T19">
-        <v>0.8826125420563383</v>
+        <v>0.892000979663465</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.14728757860505</v>
+        <v>11.47243826868254</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08403991616116288</v>
+        <v>0.08396277343326797</v>
       </c>
       <c r="C20">
-        <v>984.7831822211896</v>
+        <v>973.6497782908359</v>
       </c>
       <c r="D20">
-        <v>966.3533822211896</v>
+        <v>967.0738782908359</v>
       </c>
       <c r="E20">
-        <v>211.5802</v>
+        <v>223.4341</v>
       </c>
       <c r="F20">
-        <v>213.3702</v>
+        <v>225.2241</v>
       </c>
       <c r="G20">
         <v>231.8</v>
@@ -2927,28 +2927,28 @@
         <v>126.8</v>
       </c>
       <c r="M20">
-        <v>11.05257636</v>
+        <v>11.66660838</v>
       </c>
       <c r="N20">
-        <v>115.74742364</v>
+        <v>115.13339162</v>
       </c>
       <c r="O20">
-        <v>17.362113546</v>
+        <v>17.270008743</v>
       </c>
       <c r="P20">
-        <v>98.38531009399999</v>
+        <v>97.86338287699999</v>
       </c>
       <c r="Q20">
-        <v>109.285310094</v>
+        <v>108.763382877</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09282258068434497</v>
+        <v>0.09332972028798514</v>
       </c>
       <c r="T20">
-        <v>0.892000979663465</v>
+        <v>0.9016212305448418</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.47243826868254</v>
+        <v>10.86862572822557</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08396277343326797</v>
+        <v>0.08388563070537307</v>
       </c>
       <c r="C21">
-        <v>973.6497782908359</v>
+        <v>962.5174495404883</v>
       </c>
       <c r="D21">
-        <v>967.0738782908359</v>
+        <v>967.7954495404883</v>
       </c>
       <c r="E21">
-        <v>223.4341</v>
+        <v>235.288</v>
       </c>
       <c r="F21">
-        <v>225.2241</v>
+        <v>237.078</v>
       </c>
       <c r="G21">
         <v>231.8</v>
@@ -3009,28 +3009,28 @@
         <v>126.8</v>
       </c>
       <c r="M21">
-        <v>11.66660838</v>
+        <v>12.2806404</v>
       </c>
       <c r="N21">
-        <v>115.13339162</v>
+        <v>114.5193596</v>
       </c>
       <c r="O21">
-        <v>17.270008743</v>
+        <v>17.17790394</v>
       </c>
       <c r="P21">
-        <v>97.86338287699999</v>
+        <v>97.34145566000001</v>
       </c>
       <c r="Q21">
-        <v>108.763382877</v>
+        <v>108.24145566</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09332972028798514</v>
+        <v>0.09384953838171634</v>
       </c>
       <c r="T21">
-        <v>0.9016212305448418</v>
+        <v>0.9114819876982529</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.86862572822557</v>
+        <v>10.32519444181429</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08388563070537307</v>
+        <v>0.08380848797747815</v>
       </c>
       <c r="C22">
-        <v>962.5174495404883</v>
+        <v>951.3861983786448</v>
       </c>
       <c r="D22">
-        <v>967.7954495404883</v>
+        <v>968.5180983786448</v>
       </c>
       <c r="E22">
-        <v>235.288</v>
+        <v>247.1419</v>
       </c>
       <c r="F22">
-        <v>237.078</v>
+        <v>248.9319</v>
       </c>
       <c r="G22">
         <v>231.8</v>
@@ -3091,28 +3091,28 @@
         <v>126.8</v>
       </c>
       <c r="M22">
-        <v>12.2806404</v>
+        <v>12.89467242</v>
       </c>
       <c r="N22">
-        <v>114.5193596</v>
+        <v>113.90532758</v>
       </c>
       <c r="O22">
-        <v>17.17790394</v>
+        <v>17.085799137</v>
       </c>
       <c r="P22">
-        <v>97.34145566000001</v>
+        <v>96.81952844300001</v>
       </c>
       <c r="Q22">
-        <v>108.24145566</v>
+        <v>107.719528443</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09384953838171634</v>
+        <v>0.09438251642718753</v>
       </c>
       <c r="T22">
-        <v>0.9114819876982529</v>
+        <v>0.9215923842732695</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.32519444181429</v>
+        <v>9.833518516013608</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08380848797747815</v>
+        <v>0.08404924524958325</v>
       </c>
       <c r="C23">
-        <v>951.386198378645</v>
+        <v>937.2805233515343</v>
       </c>
       <c r="D23">
-        <v>968.5180983786448</v>
+        <v>966.2663233515342</v>
       </c>
       <c r="E23">
-        <v>247.1419</v>
+        <v>258.9958</v>
       </c>
       <c r="F23">
-        <v>248.9319</v>
+        <v>260.7858</v>
       </c>
       <c r="G23">
         <v>231.8</v>
@@ -3173,45 +3173,45 @@
         <v>126.8</v>
       </c>
       <c r="M23">
-        <v>12.89467242</v>
+        <v>13.9520403</v>
       </c>
       <c r="N23">
-        <v>113.90532758</v>
+        <v>112.8479597</v>
       </c>
       <c r="O23">
-        <v>17.085799137</v>
+        <v>16.927193955</v>
       </c>
       <c r="P23">
-        <v>96.81952844300001</v>
+        <v>95.920765745</v>
       </c>
       <c r="Q23">
-        <v>107.719528443</v>
+        <v>106.820765745</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09438251642718753</v>
+        <v>0.09492916057638878</v>
       </c>
       <c r="T23">
-        <v>0.9215923842732694</v>
+        <v>0.931962021786107</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.83351851601361</v>
+        <v>9.088276501036196</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08404924524958325</v>
+        <v>0.08398655252168834</v>
       </c>
       <c r="C24">
-        <v>937.2805233515343</v>
+        <v>926.0119723287949</v>
       </c>
       <c r="D24">
-        <v>966.2663233515342</v>
+        <v>966.8516723287947</v>
       </c>
       <c r="E24">
-        <v>258.9958</v>
+        <v>270.8497</v>
       </c>
       <c r="F24">
-        <v>260.7858</v>
+        <v>272.6397</v>
       </c>
       <c r="G24">
         <v>231.8</v>
@@ -3255,28 +3255,28 @@
         <v>126.8</v>
       </c>
       <c r="M24">
-        <v>13.9520403</v>
+        <v>14.58622395</v>
       </c>
       <c r="N24">
-        <v>112.8479597</v>
+        <v>112.21377605</v>
       </c>
       <c r="O24">
-        <v>16.927193955</v>
+        <v>16.8320664075</v>
       </c>
       <c r="P24">
-        <v>95.920765745</v>
+        <v>95.3817096425</v>
       </c>
       <c r="Q24">
-        <v>106.820765745</v>
+        <v>106.2817096425</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09492916057638878</v>
+        <v>0.09549000327491991</v>
       </c>
       <c r="T24">
-        <v>0.931962021786107</v>
+        <v>0.942601000533044</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.088276501036196</v>
+        <v>8.693134044469403</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08398655252168834</v>
+        <v>0.08392385979379344</v>
       </c>
       <c r="C25">
-        <v>926.0119723287949</v>
+        <v>914.7441309263838</v>
       </c>
       <c r="D25">
-        <v>966.8516723287947</v>
+        <v>967.4377309263839</v>
       </c>
       <c r="E25">
-        <v>270.8497</v>
+        <v>282.7036</v>
       </c>
       <c r="F25">
-        <v>272.6397</v>
+        <v>284.4936</v>
       </c>
       <c r="G25">
         <v>231.8</v>
@@ -3337,28 +3337,28 @@
         <v>126.8</v>
       </c>
       <c r="M25">
-        <v>14.58622395</v>
+        <v>15.2204076</v>
       </c>
       <c r="N25">
-        <v>112.21377605</v>
+        <v>111.5795924</v>
       </c>
       <c r="O25">
-        <v>16.8320664075</v>
+        <v>16.73693886</v>
       </c>
       <c r="P25">
-        <v>95.3817096425</v>
+        <v>94.84265354</v>
       </c>
       <c r="Q25">
-        <v>106.2817096425</v>
+        <v>105.74265354</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09549000327491991</v>
+        <v>0.09606560499183346</v>
       </c>
       <c r="T25">
-        <v>0.942601000533044</v>
+        <v>0.9535199524049005</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.693134044469403</v>
+        <v>8.330920125949845</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08392385979379342</v>
+        <v>0.08386116706589851</v>
       </c>
       <c r="C26">
-        <v>914.7441309263838</v>
+        <v>903.4770004354967</v>
       </c>
       <c r="D26">
-        <v>967.4377309263839</v>
+        <v>968.0245004354967</v>
       </c>
       <c r="E26">
-        <v>282.7035999999999</v>
+        <v>294.5574999999999</v>
       </c>
       <c r="F26">
-        <v>284.4936</v>
+        <v>296.3475</v>
       </c>
       <c r="G26">
         <v>231.8</v>
@@ -3419,28 +3419,28 @@
         <v>126.8</v>
       </c>
       <c r="M26">
-        <v>15.2204076</v>
+        <v>15.85459125</v>
       </c>
       <c r="N26">
-        <v>111.5795924</v>
+        <v>110.94540875</v>
       </c>
       <c r="O26">
-        <v>16.73693886</v>
+        <v>16.6418113125</v>
       </c>
       <c r="P26">
-        <v>94.84265354</v>
+        <v>94.3035974375</v>
       </c>
       <c r="Q26">
-        <v>105.74265354</v>
+        <v>105.2035974375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09606560499183346</v>
+        <v>0.09665655608786469</v>
       </c>
       <c r="T26">
-        <v>0.9535199524049005</v>
+        <v>0.9647300763266732</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.330920125949847</v>
+        <v>7.997683320911853</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08386116706589851</v>
+        <v>0.08379847433800362</v>
       </c>
       <c r="C27">
-        <v>903.4770004354967</v>
+        <v>892.2105821504622</v>
       </c>
       <c r="D27">
-        <v>968.0245004354967</v>
+        <v>968.6119821504622</v>
       </c>
       <c r="E27">
-        <v>294.5574999999999</v>
+        <v>306.4114</v>
       </c>
       <c r="F27">
-        <v>296.3475</v>
+        <v>308.2014</v>
       </c>
       <c r="G27">
         <v>231.8</v>
@@ -3501,28 +3501,28 @@
         <v>126.8</v>
       </c>
       <c r="M27">
-        <v>15.85459125</v>
+        <v>16.4887749</v>
       </c>
       <c r="N27">
-        <v>110.94540875</v>
+        <v>110.3112251</v>
       </c>
       <c r="O27">
-        <v>16.6418113125</v>
+        <v>16.546683765</v>
       </c>
       <c r="P27">
-        <v>94.3035974375</v>
+        <v>93.764541335</v>
       </c>
       <c r="Q27">
-        <v>105.2035974375</v>
+        <v>104.664541335</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09665655608786469</v>
+        <v>0.09726347883514003</v>
       </c>
       <c r="T27">
-        <v>0.9647300763266732</v>
+        <v>0.976243176570656</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.997683320911853</v>
+        <v>7.690080116261397</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08379847433800362</v>
+        <v>0.08391938161010871</v>
       </c>
       <c r="C28">
-        <v>892.2105821504622</v>
+        <v>879.2243206746446</v>
       </c>
       <c r="D28">
-        <v>968.6119821504622</v>
+        <v>967.4796206746446</v>
       </c>
       <c r="E28">
-        <v>306.4114</v>
+        <v>318.2653</v>
       </c>
       <c r="F28">
-        <v>308.2014</v>
+        <v>320.0553</v>
       </c>
       <c r="G28">
         <v>231.8</v>
@@ -3583,45 +3583,45 @@
         <v>126.8</v>
       </c>
       <c r="M28">
-        <v>16.4887749</v>
+        <v>17.37900279</v>
       </c>
       <c r="N28">
-        <v>110.3112251</v>
+        <v>109.42099721</v>
       </c>
       <c r="O28">
-        <v>16.546683765</v>
+        <v>16.4131495815</v>
       </c>
       <c r="P28">
-        <v>93.764541335</v>
+        <v>93.0078476285</v>
       </c>
       <c r="Q28">
-        <v>104.664541335</v>
+        <v>103.9078476285</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09726347883514003</v>
+        <v>0.09788702960288866</v>
       </c>
       <c r="T28">
-        <v>0.976243176570656</v>
+        <v>0.9880717042185836</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.15</v>
       </c>
       <c r="W28">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.690080116261397</v>
+        <v>7.296160863324195</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08391938161010871</v>
+        <v>0.08386348888221382</v>
       </c>
       <c r="C29">
-        <v>879.2243206746446</v>
+        <v>867.8935568178629</v>
       </c>
       <c r="D29">
-        <v>967.4796206746446</v>
+        <v>968.002756817863</v>
       </c>
       <c r="E29">
-        <v>318.2653</v>
+        <v>330.1192</v>
       </c>
       <c r="F29">
-        <v>320.0553</v>
+        <v>331.9092</v>
       </c>
       <c r="G29">
         <v>231.8</v>
@@ -3665,28 +3665,28 @@
         <v>126.8</v>
       </c>
       <c r="M29">
-        <v>17.37900279</v>
+        <v>18.02266956</v>
       </c>
       <c r="N29">
-        <v>109.42099721</v>
+        <v>108.77733044</v>
       </c>
       <c r="O29">
-        <v>16.4131495815</v>
+        <v>16.316599566</v>
       </c>
       <c r="P29">
-        <v>93.0078476285</v>
+        <v>92.46073087400001</v>
       </c>
       <c r="Q29">
-        <v>103.9078476285</v>
+        <v>103.360730874</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09788702960288866</v>
+        <v>0.09852790122529696</v>
       </c>
       <c r="T29">
-        <v>0.9880717042185836</v>
+        <v>1.000228802078954</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.296160863324195</v>
+        <v>7.035583689634045</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08386348888221382</v>
+        <v>0.0838075961543189</v>
       </c>
       <c r="C30">
-        <v>867.8935568178629</v>
+        <v>856.5633590081139</v>
       </c>
       <c r="D30">
-        <v>968.002756817863</v>
+        <v>968.526459008114</v>
       </c>
       <c r="E30">
-        <v>330.1192</v>
+        <v>341.9731</v>
       </c>
       <c r="F30">
-        <v>331.9092</v>
+        <v>343.7631</v>
       </c>
       <c r="G30">
         <v>231.8</v>
@@ -3747,28 +3747,28 @@
         <v>126.8</v>
       </c>
       <c r="M30">
-        <v>18.02266956</v>
+        <v>18.66633633</v>
       </c>
       <c r="N30">
-        <v>108.77733044</v>
+        <v>108.13366367</v>
       </c>
       <c r="O30">
-        <v>16.316599566</v>
+        <v>16.2200495505</v>
       </c>
       <c r="P30">
-        <v>92.46073087400001</v>
+        <v>91.91361411950001</v>
       </c>
       <c r="Q30">
-        <v>103.360730874</v>
+        <v>102.8136141195</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09852790122529696</v>
+        <v>0.09918682556946325</v>
       </c>
       <c r="T30">
-        <v>1.000228802078954</v>
+        <v>1.012728353400179</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.035583689634045</v>
+        <v>6.792977355508734</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0838075961543189</v>
+        <v>0.08375170342642399</v>
       </c>
       <c r="C31">
-        <v>856.563359008114</v>
+        <v>845.2337281646116</v>
       </c>
       <c r="D31">
-        <v>968.526459008114</v>
+        <v>969.0507281646117</v>
       </c>
       <c r="E31">
-        <v>341.9730999999999</v>
+        <v>353.8269999999999</v>
       </c>
       <c r="F31">
-        <v>343.7631</v>
+        <v>355.617</v>
       </c>
       <c r="G31">
         <v>231.8</v>
@@ -3829,28 +3829,28 @@
         <v>126.8</v>
       </c>
       <c r="M31">
-        <v>18.66633633</v>
+        <v>19.3100031</v>
       </c>
       <c r="N31">
-        <v>108.13366367</v>
+        <v>107.4899969</v>
       </c>
       <c r="O31">
-        <v>16.2200495505</v>
+        <v>16.123499535</v>
       </c>
       <c r="P31">
-        <v>91.91361411950001</v>
+        <v>91.366497365</v>
       </c>
       <c r="Q31">
-        <v>102.8136141195</v>
+        <v>102.266497365</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09918682556946325</v>
+        <v>0.09986457632346285</v>
       </c>
       <c r="T31">
-        <v>1.012728353400179</v>
+        <v>1.025585034759154</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.792977355508735</v>
+        <v>6.566544776991775</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08375170342642399</v>
+        <v>0.08369581069852909</v>
       </c>
       <c r="C32">
-        <v>845.2337281646116</v>
+        <v>833.9046652085608</v>
       </c>
       <c r="D32">
-        <v>969.0507281646117</v>
+        <v>969.5755652085609</v>
       </c>
       <c r="E32">
-        <v>353.8269999999999</v>
+        <v>365.6809</v>
       </c>
       <c r="F32">
-        <v>355.617</v>
+        <v>367.4709</v>
       </c>
       <c r="G32">
         <v>231.8</v>
@@ -3911,28 +3911,28 @@
         <v>126.8</v>
       </c>
       <c r="M32">
-        <v>19.3100031</v>
+        <v>19.95366987</v>
       </c>
       <c r="N32">
-        <v>107.4899969</v>
+        <v>106.84633013</v>
       </c>
       <c r="O32">
-        <v>16.123499535</v>
+        <v>16.0269495195</v>
       </c>
       <c r="P32">
-        <v>91.366497365</v>
+        <v>90.81938061049999</v>
       </c>
       <c r="Q32">
-        <v>102.266497365</v>
+        <v>101.7193806105</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09986457632346285</v>
+        <v>0.1005619720268538</v>
       </c>
       <c r="T32">
-        <v>1.025585034759154</v>
+        <v>1.038814373548823</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.566544776991775</v>
+        <v>6.354720751927525</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08369581069852909</v>
+        <v>0.08363991797063416</v>
       </c>
       <c r="C33">
-        <v>833.9046652085608</v>
+        <v>822.5761710631642</v>
       </c>
       <c r="D33">
-        <v>969.5755652085609</v>
+        <v>970.1009710631643</v>
       </c>
       <c r="E33">
-        <v>365.6809</v>
+        <v>377.5348</v>
       </c>
       <c r="F33">
-        <v>367.4709</v>
+        <v>379.3248</v>
       </c>
       <c r="G33">
         <v>231.8</v>
@@ -3993,28 +3993,28 @@
         <v>126.8</v>
       </c>
       <c r="M33">
-        <v>19.95366987</v>
+        <v>20.59733664</v>
       </c>
       <c r="N33">
-        <v>106.84633013</v>
+        <v>106.20266336</v>
       </c>
       <c r="O33">
-        <v>16.0269495195</v>
+        <v>15.930399504</v>
       </c>
       <c r="P33">
-        <v>90.81938061049999</v>
+        <v>90.272263856</v>
       </c>
       <c r="Q33">
-        <v>101.7193806105</v>
+        <v>101.172263856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1005619720268538</v>
+        <v>0.1012798793685797</v>
       </c>
       <c r="T33">
-        <v>1.038814373548823</v>
+        <v>1.052432810538189</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.354720751927525</v>
+        <v>6.15613572842979</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08363991797063416</v>
+        <v>0.08386452524273927</v>
       </c>
       <c r="C34">
-        <v>822.5761710631642</v>
+        <v>808.6143517026194</v>
       </c>
       <c r="D34">
-        <v>970.1009710631643</v>
+        <v>967.9930517026193</v>
       </c>
       <c r="E34">
-        <v>377.5348</v>
+        <v>389.3887</v>
       </c>
       <c r="F34">
-        <v>379.3248</v>
+        <v>391.1787</v>
       </c>
       <c r="G34">
         <v>231.8</v>
@@ -4075,45 +4075,45 @@
         <v>126.8</v>
       </c>
       <c r="M34">
-        <v>20.59733664</v>
+        <v>21.63218211</v>
       </c>
       <c r="N34">
-        <v>106.20266336</v>
+        <v>105.16781789</v>
       </c>
       <c r="O34">
-        <v>15.930399504</v>
+        <v>15.7751726835</v>
       </c>
       <c r="P34">
-        <v>90.272263856</v>
+        <v>89.39264520649999</v>
       </c>
       <c r="Q34">
-        <v>101.172263856</v>
+        <v>100.2926452065</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1012798793685797</v>
+        <v>0.1020192167802079</v>
       </c>
       <c r="T34">
-        <v>1.052432810538189</v>
+        <v>1.0664577680347</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.15613572842979</v>
+        <v>5.86163704406795</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08386452524273927</v>
+        <v>0.08381713251484435</v>
       </c>
       <c r="C35">
-        <v>808.6143517026194</v>
+        <v>797.2044653819862</v>
       </c>
       <c r="D35">
-        <v>967.9930517026193</v>
+        <v>968.4370653819863</v>
       </c>
       <c r="E35">
-        <v>389.3887</v>
+        <v>401.2426</v>
       </c>
       <c r="F35">
-        <v>391.1787</v>
+        <v>403.0326</v>
       </c>
       <c r="G35">
         <v>231.8</v>
@@ -4157,28 +4157,28 @@
         <v>126.8</v>
       </c>
       <c r="M35">
-        <v>21.63218211</v>
+        <v>22.28770278</v>
       </c>
       <c r="N35">
-        <v>105.16781789</v>
+        <v>104.51229722</v>
       </c>
       <c r="O35">
-        <v>15.7751726835</v>
+        <v>15.676844583</v>
       </c>
       <c r="P35">
-        <v>89.39264520649999</v>
+        <v>88.835452637</v>
       </c>
       <c r="Q35">
-        <v>100.2926452065</v>
+        <v>99.73545263699999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1020192167802079</v>
+        <v>0.1027809583558248</v>
       </c>
       <c r="T35">
-        <v>1.0664577680347</v>
+        <v>1.080907724243227</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.86163704406795</v>
+        <v>5.68923595453654</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08381713251484435</v>
+        <v>0.08376973978694946</v>
       </c>
       <c r="C36">
-        <v>797.2044653819862</v>
+        <v>785.7949865820876</v>
       </c>
       <c r="D36">
-        <v>968.4370653819863</v>
+        <v>968.8814865820876</v>
       </c>
       <c r="E36">
-        <v>401.2426</v>
+        <v>413.0965</v>
       </c>
       <c r="F36">
-        <v>403.0326</v>
+        <v>414.8865</v>
       </c>
       <c r="G36">
         <v>231.8</v>
@@ -4239,28 +4239,28 @@
         <v>126.8</v>
       </c>
       <c r="M36">
-        <v>22.28770278</v>
+        <v>22.94322345</v>
       </c>
       <c r="N36">
-        <v>104.51229722</v>
+        <v>103.85677655</v>
       </c>
       <c r="O36">
-        <v>15.676844583</v>
+        <v>15.5785164825</v>
       </c>
       <c r="P36">
-        <v>88.835452637</v>
+        <v>88.2782600675</v>
       </c>
       <c r="Q36">
-        <v>99.73545263699999</v>
+        <v>99.17826006749999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1027809583558248</v>
+        <v>0.1035661381337684</v>
       </c>
       <c r="T36">
-        <v>1.080907724243227</v>
+        <v>1.095802294488939</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.68923595453654</v>
+        <v>5.526686355835496</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08376973978694946</v>
+        <v>0.08372234705905454</v>
       </c>
       <c r="C37">
-        <v>785.7949865820876</v>
+        <v>774.3859158642225</v>
       </c>
       <c r="D37">
-        <v>968.8814865820876</v>
+        <v>969.3263158642225</v>
       </c>
       <c r="E37">
-        <v>413.0965</v>
+        <v>424.9504</v>
       </c>
       <c r="F37">
-        <v>414.8865</v>
+        <v>426.7404</v>
       </c>
       <c r="G37">
         <v>231.8</v>
@@ -4321,28 +4321,28 @@
         <v>126.8</v>
       </c>
       <c r="M37">
-        <v>22.94322345</v>
+        <v>23.59874412</v>
       </c>
       <c r="N37">
-        <v>103.85677655</v>
+        <v>103.20125588</v>
       </c>
       <c r="O37">
-        <v>15.5785164825</v>
+        <v>15.480188382</v>
       </c>
       <c r="P37">
-        <v>88.2782600675</v>
+        <v>87.721067498</v>
       </c>
       <c r="Q37">
-        <v>99.17826006749999</v>
+        <v>98.62106749799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1035661381337684</v>
+        <v>0.1043758547797727</v>
       </c>
       <c r="T37">
-        <v>1.095802294488939</v>
+        <v>1.111162320054829</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.526686355835496</v>
+        <v>5.37316729039562</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08372234705905456</v>
+        <v>0.08367495433115965</v>
       </c>
       <c r="C38">
-        <v>774.3859158642224</v>
+        <v>762.9772537907195</v>
       </c>
       <c r="D38">
-        <v>969.3263158642222</v>
+        <v>969.7715537907195</v>
       </c>
       <c r="E38">
-        <v>424.9503999999999</v>
+        <v>436.8043</v>
       </c>
       <c r="F38">
-        <v>426.7404</v>
+        <v>438.5943</v>
       </c>
       <c r="G38">
         <v>231.8</v>
@@ -4403,28 +4403,28 @@
         <v>126.8</v>
       </c>
       <c r="M38">
-        <v>23.59874412</v>
+        <v>24.25426479</v>
       </c>
       <c r="N38">
-        <v>103.20125588</v>
+        <v>102.54573521</v>
       </c>
       <c r="O38">
-        <v>15.480188382</v>
+        <v>15.3818602815</v>
       </c>
       <c r="P38">
-        <v>87.721067498</v>
+        <v>87.16387492850001</v>
       </c>
       <c r="Q38">
-        <v>98.62106749799999</v>
+        <v>98.0638749285</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1043758547797727</v>
+        <v>0.1052112767161264</v>
       </c>
       <c r="T38">
-        <v>1.111162320054829</v>
+        <v>1.127009965479954</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.373167290395621</v>
+        <v>5.227946552817361</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08367495433115965</v>
+        <v>0.08362756160326473</v>
       </c>
       <c r="C39">
-        <v>762.9772537907195</v>
+        <v>751.5690009249423</v>
       </c>
       <c r="D39">
-        <v>969.7715537907195</v>
+        <v>970.2172009249423</v>
       </c>
       <c r="E39">
-        <v>436.8043</v>
+        <v>448.6581999999999</v>
       </c>
       <c r="F39">
-        <v>438.5943</v>
+        <v>450.4481999999999</v>
       </c>
       <c r="G39">
         <v>231.8</v>
@@ -4485,28 +4485,28 @@
         <v>126.8</v>
       </c>
       <c r="M39">
-        <v>24.25426479</v>
+        <v>24.90978546</v>
       </c>
       <c r="N39">
-        <v>102.54573521</v>
+        <v>101.89021454</v>
       </c>
       <c r="O39">
-        <v>15.3818602815</v>
+        <v>15.283532181</v>
       </c>
       <c r="P39">
-        <v>87.16387492850001</v>
+        <v>86.606682359</v>
       </c>
       <c r="Q39">
-        <v>98.0638749285</v>
+        <v>97.506682359</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1052112767161264</v>
+        <v>0.1060736477472012</v>
       </c>
       <c r="T39">
-        <v>1.127009965479954</v>
+        <v>1.143368825273632</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.227946552817361</v>
+        <v>5.090369011953747</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08362756160326473</v>
+        <v>0.08358016887536983</v>
       </c>
       <c r="C40">
-        <v>751.5690009249423</v>
+        <v>740.1611578312904</v>
       </c>
       <c r="D40">
-        <v>970.2172009249423</v>
+        <v>970.6632578312903</v>
       </c>
       <c r="E40">
-        <v>448.6581999999999</v>
+        <v>460.5120999999999</v>
       </c>
       <c r="F40">
-        <v>450.4481999999999</v>
+        <v>462.3020999999999</v>
       </c>
       <c r="G40">
         <v>231.8</v>
@@ -4567,28 +4567,28 @@
         <v>126.8</v>
       </c>
       <c r="M40">
-        <v>24.90978546</v>
+        <v>25.56530613</v>
       </c>
       <c r="N40">
-        <v>101.89021454</v>
+        <v>101.23469387</v>
       </c>
       <c r="O40">
-        <v>15.283532181</v>
+        <v>15.1852040805</v>
       </c>
       <c r="P40">
-        <v>86.606682359</v>
+        <v>86.0494897895</v>
       </c>
       <c r="Q40">
-        <v>97.506682359</v>
+        <v>96.94948978949999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1060736477472012</v>
+        <v>0.1069642932383112</v>
       </c>
       <c r="T40">
-        <v>1.143368825273632</v>
+        <v>1.160264041126118</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.090369011953747</v>
+        <v>4.959846729595959</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08358016887536983</v>
+        <v>0.08353277614747492</v>
       </c>
       <c r="C41">
-        <v>740.1611578312904</v>
+        <v>728.7537250752005</v>
       </c>
       <c r="D41">
-        <v>970.6632578312903</v>
+        <v>971.1097250752005</v>
       </c>
       <c r="E41">
-        <v>460.5120999999999</v>
+        <v>472.3659999999999</v>
       </c>
       <c r="F41">
-        <v>462.3020999999999</v>
+        <v>474.1559999999999</v>
       </c>
       <c r="G41">
         <v>231.8</v>
@@ -4649,28 +4649,28 @@
         <v>126.8</v>
       </c>
       <c r="M41">
-        <v>25.56530613</v>
+        <v>26.2208268</v>
       </c>
       <c r="N41">
-        <v>101.23469387</v>
+        <v>100.5791732</v>
       </c>
       <c r="O41">
-        <v>15.1852040805</v>
+        <v>15.08687598</v>
       </c>
       <c r="P41">
-        <v>86.0494897895</v>
+        <v>85.49229722</v>
       </c>
       <c r="Q41">
-        <v>96.94948978949999</v>
+        <v>96.39229721999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1069642932383112</v>
+        <v>0.1078846269124582</v>
       </c>
       <c r="T41">
-        <v>1.160264041126118</v>
+        <v>1.177722430840354</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.959846729595959</v>
+        <v>4.835850561356059</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08353277614747492</v>
+        <v>0.08348538341958002</v>
       </c>
       <c r="C42">
-        <v>728.7537250752005</v>
+        <v>717.3467032231515</v>
       </c>
       <c r="D42">
-        <v>971.1097250752005</v>
+        <v>971.5566032231516</v>
       </c>
       <c r="E42">
-        <v>472.3659999999999</v>
+        <v>484.2198999999999</v>
       </c>
       <c r="F42">
-        <v>474.1559999999999</v>
+        <v>486.0099</v>
       </c>
       <c r="G42">
         <v>231.8</v>
@@ -4731,28 +4731,28 @@
         <v>126.8</v>
       </c>
       <c r="M42">
-        <v>26.2208268</v>
+        <v>26.87634747</v>
       </c>
       <c r="N42">
-        <v>100.5791732</v>
+        <v>99.92365253</v>
       </c>
       <c r="O42">
-        <v>15.08687598</v>
+        <v>14.9885478795</v>
       </c>
       <c r="P42">
-        <v>85.49229722</v>
+        <v>84.93510465049999</v>
       </c>
       <c r="Q42">
-        <v>96.39229721999999</v>
+        <v>95.83510465049999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1078846269124582</v>
+        <v>0.1088361583382712</v>
       </c>
       <c r="T42">
-        <v>1.177722430840354</v>
+        <v>1.195772630375412</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.835850561356059</v>
+        <v>4.717902986688838</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08348538341958002</v>
+        <v>0.0834379906916851</v>
       </c>
       <c r="C43">
-        <v>717.3467032231515</v>
+        <v>705.9400928426652</v>
       </c>
       <c r="D43">
-        <v>971.5566032231516</v>
+        <v>972.0038928426652</v>
       </c>
       <c r="E43">
-        <v>484.2198999999999</v>
+        <v>496.0737999999999</v>
       </c>
       <c r="F43">
-        <v>486.0099</v>
+        <v>497.8638</v>
       </c>
       <c r="G43">
         <v>231.8</v>
@@ -4813,28 +4813,28 @@
         <v>126.8</v>
       </c>
       <c r="M43">
-        <v>26.87634747</v>
+        <v>27.53186814</v>
       </c>
       <c r="N43">
-        <v>99.92365253</v>
+        <v>99.26813186</v>
       </c>
       <c r="O43">
-        <v>14.9885478795</v>
+        <v>14.890219779</v>
       </c>
       <c r="P43">
-        <v>84.93510465049999</v>
+        <v>84.37791208100001</v>
       </c>
       <c r="Q43">
-        <v>95.83510465049999</v>
+        <v>95.277912081</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1088361583382712</v>
+        <v>0.1098205011925605</v>
       </c>
       <c r="T43">
-        <v>1.195772630375412</v>
+        <v>1.214445250584093</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.717902986688838</v>
+        <v>4.605571963196247</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08343799069168512</v>
+        <v>0.08430434796379022</v>
       </c>
       <c r="C44">
-        <v>705.9400928426653</v>
+        <v>685.9740740166803</v>
       </c>
       <c r="D44">
-        <v>972.0038928426652</v>
+        <v>963.8917740166802</v>
       </c>
       <c r="E44">
-        <v>496.0737999999999</v>
+        <v>507.9276999999999</v>
       </c>
       <c r="F44">
-        <v>497.8637999999999</v>
+        <v>509.7176999999999</v>
       </c>
       <c r="G44">
         <v>231.8</v>
@@ -4895,45 +4895,45 @@
         <v>126.8</v>
       </c>
       <c r="M44">
-        <v>27.53186814</v>
+        <v>29.46168306</v>
       </c>
       <c r="N44">
-        <v>99.26813186</v>
+        <v>97.33831694</v>
       </c>
       <c r="O44">
-        <v>14.890219779</v>
+        <v>14.600747541</v>
       </c>
       <c r="P44">
-        <v>84.37791208100001</v>
+        <v>82.73756939899999</v>
       </c>
       <c r="Q44">
-        <v>95.277912081</v>
+        <v>93.63756939899999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1098205011925605</v>
+        <v>0.1108393823926144</v>
       </c>
       <c r="T44">
-        <v>1.214445250584092</v>
+        <v>1.233773050449218</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.605571963196248</v>
+        <v>4.303895325388108</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08430434796379022</v>
+        <v>0.0842782052358953</v>
       </c>
       <c r="C45">
-        <v>685.9740740166803</v>
+        <v>674.3629791342394</v>
       </c>
       <c r="D45">
-        <v>963.8917740166802</v>
+        <v>964.1345791342394</v>
       </c>
       <c r="E45">
-        <v>507.9276999999999</v>
+        <v>519.7816</v>
       </c>
       <c r="F45">
-        <v>509.7176999999999</v>
+        <v>521.5716</v>
       </c>
       <c r="G45">
         <v>231.8</v>
@@ -4977,28 +4977,28 @@
         <v>126.8</v>
       </c>
       <c r="M45">
-        <v>29.46168306</v>
+        <v>30.14683848</v>
       </c>
       <c r="N45">
-        <v>97.33831694</v>
+        <v>96.65316152</v>
       </c>
       <c r="O45">
-        <v>14.600747541</v>
+        <v>14.497974228</v>
       </c>
       <c r="P45">
-        <v>82.73756939899999</v>
+        <v>82.15518729199999</v>
       </c>
       <c r="Q45">
-        <v>93.63756939899999</v>
+        <v>93.05518729199999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1108393823926144</v>
+        <v>0.1118946522069559</v>
       </c>
       <c r="T45">
-        <v>1.233773050449218</v>
+        <v>1.253791128880955</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.303895325388108</v>
+        <v>4.206079522538378</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0842782052358953</v>
+        <v>0.08425206250800039</v>
       </c>
       <c r="C46">
-        <v>674.3629791342394</v>
+        <v>662.7520066082312</v>
       </c>
       <c r="D46">
-        <v>964.1345791342394</v>
+        <v>964.3775066082311</v>
       </c>
       <c r="E46">
-        <v>519.7816</v>
+        <v>531.6355</v>
       </c>
       <c r="F46">
-        <v>521.5716</v>
+        <v>533.4254999999999</v>
       </c>
       <c r="G46">
         <v>231.8</v>
@@ -5059,28 +5059,28 @@
         <v>126.8</v>
       </c>
       <c r="M46">
-        <v>30.14683848</v>
+        <v>30.8319939</v>
       </c>
       <c r="N46">
-        <v>96.65316152</v>
+        <v>95.9680061</v>
       </c>
       <c r="O46">
-        <v>14.497974228</v>
+        <v>14.395200915</v>
       </c>
       <c r="P46">
-        <v>82.15518729199999</v>
+        <v>81.57280518499999</v>
       </c>
       <c r="Q46">
-        <v>93.05518729199999</v>
+        <v>92.47280518499998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1118946522069559</v>
+        <v>0.1129882954690916</v>
       </c>
       <c r="T46">
-        <v>1.253791128880955</v>
+        <v>1.274537137437482</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.206079522538378</v>
+        <v>4.112611088704192</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08425206250800039</v>
+        <v>0.08422591978010549</v>
       </c>
       <c r="C47">
-        <v>662.7520066082312</v>
+        <v>651.1411565311672</v>
       </c>
       <c r="D47">
-        <v>964.3775066082311</v>
+        <v>964.6205565311673</v>
       </c>
       <c r="E47">
-        <v>531.6355</v>
+        <v>543.4894</v>
       </c>
       <c r="F47">
-        <v>533.4254999999999</v>
+        <v>545.2794</v>
       </c>
       <c r="G47">
         <v>231.8</v>
@@ -5141,28 +5141,28 @@
         <v>126.8</v>
       </c>
       <c r="M47">
-        <v>30.8319939</v>
+        <v>31.51714932</v>
       </c>
       <c r="N47">
-        <v>95.9680061</v>
+        <v>95.28285068</v>
       </c>
       <c r="O47">
-        <v>14.395200915</v>
+        <v>14.292427602</v>
       </c>
       <c r="P47">
-        <v>81.57280518499999</v>
+        <v>80.99042307799999</v>
       </c>
       <c r="Q47">
-        <v>92.47280518499998</v>
+        <v>91.89042307799998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1129882954690916</v>
+        <v>0.1141224440372324</v>
       </c>
       <c r="T47">
-        <v>1.274537137437482</v>
+        <v>1.296051516681288</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.112611088704192</v>
+        <v>4.023206499819318</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08422591978010549</v>
+        <v>0.08559802705221058</v>
       </c>
       <c r="C48">
-        <v>651.1411565311672</v>
+        <v>626.6940878312346</v>
       </c>
       <c r="D48">
-        <v>964.6205565311673</v>
+        <v>952.0273878312346</v>
       </c>
       <c r="E48">
-        <v>543.4894</v>
+        <v>555.3433</v>
       </c>
       <c r="F48">
-        <v>545.2794</v>
+        <v>557.1333</v>
       </c>
       <c r="G48">
         <v>231.8</v>
@@ -5223,45 +5223,45 @@
         <v>126.8</v>
       </c>
       <c r="M48">
-        <v>31.51714932</v>
+        <v>34.15227128999999</v>
       </c>
       <c r="N48">
-        <v>95.28285068</v>
+        <v>92.64772871</v>
       </c>
       <c r="O48">
-        <v>14.292427602</v>
+        <v>13.8971593065</v>
       </c>
       <c r="P48">
-        <v>80.99042307799999</v>
+        <v>78.75056940349999</v>
       </c>
       <c r="Q48">
-        <v>91.89042307799998</v>
+        <v>89.65056940349999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1141224440372324</v>
+        <v>0.1152993906645483</v>
       </c>
       <c r="T48">
-        <v>1.296051516681288</v>
+        <v>1.318377759292785</v>
       </c>
       <c r="U48">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.023206499819318</v>
+        <v>3.712783812335429</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08559802705221058</v>
+        <v>0.08560163432431568</v>
       </c>
       <c r="C49">
-        <v>626.6940878312346</v>
+        <v>614.8075137125136</v>
       </c>
       <c r="D49">
-        <v>952.0273878312346</v>
+        <v>951.9947137125137</v>
       </c>
       <c r="E49">
-        <v>555.3433</v>
+        <v>567.1972000000001</v>
       </c>
       <c r="F49">
-        <v>557.1333</v>
+        <v>568.9872</v>
       </c>
       <c r="G49">
         <v>231.8</v>
@@ -5305,28 +5305,28 @@
         <v>126.8</v>
       </c>
       <c r="M49">
-        <v>34.15227128999999</v>
+        <v>34.87891536</v>
       </c>
       <c r="N49">
-        <v>92.64772871</v>
+        <v>91.92108464</v>
       </c>
       <c r="O49">
-        <v>13.8971593065</v>
+        <v>13.788162696</v>
       </c>
       <c r="P49">
-        <v>78.75056940349999</v>
+        <v>78.132921944</v>
       </c>
       <c r="Q49">
-        <v>89.65056940349999</v>
+        <v>89.03292194399999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1152993906645483</v>
+        <v>0.1165216044698378</v>
       </c>
       <c r="T49">
-        <v>1.318377759292785</v>
+        <v>1.341562703543186</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.712783812335429</v>
+        <v>3.63543414957844</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08560163432431568</v>
+        <v>0.08560524159642077</v>
       </c>
       <c r="C50">
-        <v>614.8075137125137</v>
+        <v>602.9209418365043</v>
       </c>
       <c r="D50">
-        <v>951.9947137125137</v>
+        <v>951.9620418365043</v>
       </c>
       <c r="E50">
-        <v>567.1972</v>
+        <v>579.0511</v>
       </c>
       <c r="F50">
-        <v>568.9871999999999</v>
+        <v>580.8411</v>
       </c>
       <c r="G50">
         <v>231.8</v>
@@ -5387,28 +5387,28 @@
         <v>126.8</v>
       </c>
       <c r="M50">
-        <v>34.87891535999999</v>
+        <v>35.60555943</v>
       </c>
       <c r="N50">
-        <v>91.92108464</v>
+        <v>91.19444057</v>
       </c>
       <c r="O50">
-        <v>13.788162696</v>
+        <v>13.6791660855</v>
       </c>
       <c r="P50">
-        <v>78.132921944</v>
+        <v>77.5152744845</v>
       </c>
       <c r="Q50">
-        <v>89.03292194399999</v>
+        <v>88.41527448449999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1165216044698378</v>
+        <v>0.117791748228276</v>
       </c>
       <c r="T50">
-        <v>1.341562703543186</v>
+        <v>1.365656861293602</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.635434149578441</v>
+        <v>3.561241615913574</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08560524159642077</v>
+        <v>0.08679884886852586</v>
       </c>
       <c r="C51">
-        <v>602.9209418365043</v>
+        <v>580.3780264643281</v>
       </c>
       <c r="D51">
-        <v>951.9620418365043</v>
+        <v>941.273026464328</v>
       </c>
       <c r="E51">
-        <v>579.0511</v>
+        <v>590.905</v>
       </c>
       <c r="F51">
-        <v>580.8411</v>
+        <v>592.6949999999999</v>
       </c>
       <c r="G51">
         <v>231.8</v>
@@ -5469,45 +5469,45 @@
         <v>126.8</v>
       </c>
       <c r="M51">
-        <v>35.60555943</v>
+        <v>37.9917495</v>
       </c>
       <c r="N51">
-        <v>91.19444057</v>
+        <v>88.8082505</v>
       </c>
       <c r="O51">
-        <v>13.6791660855</v>
+        <v>13.321237575</v>
       </c>
       <c r="P51">
-        <v>77.5152744845</v>
+        <v>75.487012925</v>
       </c>
       <c r="Q51">
-        <v>88.41527448449999</v>
+        <v>86.38701292499999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.117791748228276</v>
+        <v>0.1191126977370517</v>
       </c>
       <c r="T51">
-        <v>1.365656861293602</v>
+        <v>1.390714785354036</v>
       </c>
       <c r="U51">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.561241615913574</v>
+        <v>3.337566752486615</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08679884886852586</v>
+        <v>0.08682625614063096</v>
       </c>
       <c r="C52">
-        <v>580.3780264643281</v>
+        <v>568.2815067528408</v>
       </c>
       <c r="D52">
-        <v>941.273026464328</v>
+        <v>941.0304067528407</v>
       </c>
       <c r="E52">
-        <v>590.905</v>
+        <v>602.7588999999999</v>
       </c>
       <c r="F52">
-        <v>592.6949999999999</v>
+        <v>604.5488999999999</v>
       </c>
       <c r="G52">
         <v>231.8</v>
@@ -5551,28 +5551,28 @@
         <v>126.8</v>
       </c>
       <c r="M52">
-        <v>37.9917495</v>
+        <v>38.75158448999999</v>
       </c>
       <c r="N52">
-        <v>88.8082505</v>
+        <v>88.04841551000001</v>
       </c>
       <c r="O52">
-        <v>13.321237575</v>
+        <v>13.2072623265</v>
       </c>
       <c r="P52">
-        <v>75.487012925</v>
+        <v>74.84115318350001</v>
       </c>
       <c r="Q52">
-        <v>86.38701292499999</v>
+        <v>85.7411531835</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1191126977370517</v>
+        <v>0.1204875635523081</v>
       </c>
       <c r="T52">
-        <v>1.390714785354036</v>
+        <v>1.416795481825099</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.337566752486615</v>
+        <v>3.272124267143742</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08682625614063096</v>
+        <v>0.08685366341273604</v>
       </c>
       <c r="C53">
-        <v>568.2815067528408</v>
+        <v>556.1851120829812</v>
       </c>
       <c r="D53">
-        <v>941.0304067528407</v>
+        <v>940.7879120829811</v>
       </c>
       <c r="E53">
-        <v>602.7588999999999</v>
+        <v>614.6128</v>
       </c>
       <c r="F53">
-        <v>604.5488999999999</v>
+        <v>616.4028</v>
       </c>
       <c r="G53">
         <v>231.8</v>
@@ -5633,28 +5633,28 @@
         <v>126.8</v>
       </c>
       <c r="M53">
-        <v>38.75158448999999</v>
+        <v>39.51141948</v>
       </c>
       <c r="N53">
-        <v>88.04841551000001</v>
+        <v>87.28858052</v>
       </c>
       <c r="O53">
-        <v>13.2072623265</v>
+        <v>13.093287078</v>
       </c>
       <c r="P53">
-        <v>74.84115318350001</v>
+        <v>74.19529344199999</v>
       </c>
       <c r="Q53">
-        <v>85.7411531835</v>
+        <v>85.09529344199998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1204875635523081</v>
+        <v>0.1219197154432001</v>
       </c>
       <c r="T53">
-        <v>1.416795481825099</v>
+        <v>1.443962873982456</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.272124267143742</v>
+        <v>3.209198800467899</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08685366341273604</v>
+        <v>0.08688107068484113</v>
       </c>
       <c r="C54">
-        <v>556.1851120829812</v>
+        <v>544.0888423581077</v>
       </c>
       <c r="D54">
-        <v>940.7879120829811</v>
+        <v>940.5455423581076</v>
       </c>
       <c r="E54">
-        <v>614.6128</v>
+        <v>626.4666999999999</v>
       </c>
       <c r="F54">
-        <v>616.4028</v>
+        <v>628.2566999999999</v>
       </c>
       <c r="G54">
         <v>231.8</v>
@@ -5715,28 +5715,28 @@
         <v>126.8</v>
       </c>
       <c r="M54">
-        <v>39.51141948</v>
+        <v>40.27125447</v>
       </c>
       <c r="N54">
-        <v>87.28858052</v>
+        <v>86.52874553000001</v>
       </c>
       <c r="O54">
-        <v>13.093287078</v>
+        <v>12.9793118295</v>
       </c>
       <c r="P54">
-        <v>74.19529344199999</v>
+        <v>73.5494337005</v>
       </c>
       <c r="Q54">
-        <v>85.09529344199998</v>
+        <v>84.44943370049999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1219197154432001</v>
+        <v>0.1234128099677471</v>
       </c>
       <c r="T54">
-        <v>1.443962873982456</v>
+        <v>1.472286325380552</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.209198800467899</v>
+        <v>3.148647879704355</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08688107068484113</v>
+        <v>0.08690847795694623</v>
       </c>
       <c r="C55">
-        <v>544.0888423581077</v>
+        <v>531.9926974816788</v>
       </c>
       <c r="D55">
-        <v>940.5455423581076</v>
+        <v>940.3032974816788</v>
       </c>
       <c r="E55">
-        <v>626.4666999999999</v>
+        <v>638.3206</v>
       </c>
       <c r="F55">
-        <v>628.2566999999999</v>
+        <v>640.1106</v>
       </c>
       <c r="G55">
         <v>231.8</v>
@@ -5797,28 +5797,28 @@
         <v>126.8</v>
       </c>
       <c r="M55">
-        <v>40.27125447</v>
+        <v>41.03108946</v>
       </c>
       <c r="N55">
-        <v>86.52874553000001</v>
+        <v>85.76891053999999</v>
       </c>
       <c r="O55">
-        <v>12.9793118295</v>
+        <v>12.865336581</v>
       </c>
       <c r="P55">
-        <v>73.5494337005</v>
+        <v>72.903573959</v>
       </c>
       <c r="Q55">
-        <v>84.44943370049999</v>
+        <v>83.80357395899999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1234128099677471</v>
+        <v>0.1249708216455353</v>
       </c>
       <c r="T55">
-        <v>1.472286325380552</v>
+        <v>1.50184123118726</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.148647879704355</v>
+        <v>3.090339585635755</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08690847795694623</v>
+        <v>0.08693588522905132</v>
       </c>
       <c r="C56">
-        <v>531.9926974816788</v>
+        <v>519.8966773572525</v>
       </c>
       <c r="D56">
-        <v>940.3032974816788</v>
+        <v>940.0611773572524</v>
       </c>
       <c r="E56">
-        <v>638.3206</v>
+        <v>650.1745</v>
       </c>
       <c r="F56">
-        <v>640.1106</v>
+        <v>651.9644999999999</v>
       </c>
       <c r="G56">
         <v>231.8</v>
@@ -5879,28 +5879,28 @@
         <v>126.8</v>
       </c>
       <c r="M56">
-        <v>41.03108946</v>
+        <v>41.79092445</v>
       </c>
       <c r="N56">
-        <v>85.76891053999999</v>
+        <v>85.00907555000001</v>
       </c>
       <c r="O56">
-        <v>12.865336581</v>
+        <v>12.7513613325</v>
       </c>
       <c r="P56">
-        <v>72.903573959</v>
+        <v>72.25771421750001</v>
       </c>
       <c r="Q56">
-        <v>83.80357395899999</v>
+        <v>83.1577142175</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1249708216455353</v>
+        <v>0.1265980782867807</v>
       </c>
       <c r="T56">
-        <v>1.50184123118726</v>
+        <v>1.532709688363156</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.090339585635755</v>
+        <v>3.034151593169651</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08693588522905132</v>
+        <v>0.09067609250115642</v>
       </c>
       <c r="C57">
-        <v>519.8966773572525</v>
+        <v>476.1310642379063</v>
       </c>
       <c r="D57">
-        <v>940.0611773572524</v>
+        <v>908.1494642379063</v>
       </c>
       <c r="E57">
-        <v>650.1745</v>
+        <v>662.0284</v>
       </c>
       <c r="F57">
-        <v>651.9644999999999</v>
+        <v>663.8184</v>
       </c>
       <c r="G57">
         <v>231.8</v>
@@ -5961,45 +5961,45 @@
         <v>126.8</v>
       </c>
       <c r="M57">
-        <v>41.79092445</v>
+        <v>47.72854296000001</v>
       </c>
       <c r="N57">
-        <v>85.00907555000001</v>
+        <v>79.07145703999998</v>
       </c>
       <c r="O57">
-        <v>12.7513613325</v>
+        <v>11.860718556</v>
       </c>
       <c r="P57">
-        <v>72.25771421750001</v>
+        <v>67.21073848399999</v>
       </c>
       <c r="Q57">
-        <v>83.1577142175</v>
+        <v>78.11073848399998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1265980782867807</v>
+        <v>0.1282993011389919</v>
       </c>
       <c r="T57">
-        <v>1.532709688363156</v>
+        <v>1.564981257228866</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.15</v>
       </c>
       <c r="W57">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.034151593169651</v>
+        <v>2.65669119851967</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09067609250115642</v>
+        <v>0.09076979977326152</v>
       </c>
       <c r="C58">
-        <v>476.1310642379063</v>
+        <v>463.5054442487617</v>
       </c>
       <c r="D58">
-        <v>908.1494642379063</v>
+        <v>907.3777442487616</v>
       </c>
       <c r="E58">
-        <v>662.0284</v>
+        <v>673.8823</v>
       </c>
       <c r="F58">
-        <v>663.8184</v>
+        <v>675.6723</v>
       </c>
       <c r="G58">
         <v>231.8</v>
@@ -6043,28 +6043,28 @@
         <v>126.8</v>
       </c>
       <c r="M58">
-        <v>47.72854296000001</v>
+        <v>48.58083837</v>
       </c>
       <c r="N58">
-        <v>79.07145703999998</v>
+        <v>78.21916163</v>
       </c>
       <c r="O58">
-        <v>11.860718556</v>
+        <v>11.7328742445</v>
       </c>
       <c r="P58">
-        <v>67.21073848399999</v>
+        <v>66.48628738550001</v>
       </c>
       <c r="Q58">
-        <v>78.11073848399998</v>
+        <v>77.3862873855</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1282993011389919</v>
+        <v>0.1300796506354919</v>
       </c>
       <c r="T58">
-        <v>1.564981257228866</v>
+        <v>1.598753829297631</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.65669119851967</v>
+        <v>2.610082581001782</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09076979977326152</v>
+        <v>0.09086350704536661</v>
       </c>
       <c r="C59">
-        <v>463.5054442487617</v>
+        <v>450.8811347181079</v>
       </c>
       <c r="D59">
-        <v>907.3777442487616</v>
+        <v>906.6073347181079</v>
       </c>
       <c r="E59">
-        <v>673.8823</v>
+        <v>685.7362000000001</v>
       </c>
       <c r="F59">
-        <v>675.6723</v>
+        <v>687.5262</v>
       </c>
       <c r="G59">
         <v>231.8</v>
@@ -6125,28 +6125,28 @@
         <v>126.8</v>
       </c>
       <c r="M59">
-        <v>48.58083837</v>
+        <v>49.43313378000001</v>
       </c>
       <c r="N59">
-        <v>78.21916163</v>
+        <v>77.36686621999999</v>
       </c>
       <c r="O59">
-        <v>11.7328742445</v>
+        <v>11.605029933</v>
       </c>
       <c r="P59">
-        <v>66.48628738550001</v>
+        <v>65.76183628699999</v>
       </c>
       <c r="Q59">
-        <v>77.3862873855</v>
+        <v>76.66183628699999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1300796506354919</v>
+        <v>0.1319447786794443</v>
       </c>
       <c r="T59">
-        <v>1.598753829297631</v>
+        <v>1.634134619083957</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.610082581001782</v>
+        <v>2.565081157191406</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09086350704536661</v>
+        <v>0.0909572143174717</v>
       </c>
       <c r="C60">
-        <v>450.881134718108</v>
+        <v>438.2581323108404</v>
       </c>
       <c r="D60">
-        <v>906.6073347181079</v>
+        <v>905.8382323108402</v>
       </c>
       <c r="E60">
-        <v>685.7361999999999</v>
+        <v>697.5900999999999</v>
       </c>
       <c r="F60">
-        <v>687.5261999999999</v>
+        <v>699.3800999999999</v>
       </c>
       <c r="G60">
         <v>231.8</v>
@@ -6207,28 +6207,28 @@
         <v>126.8</v>
       </c>
       <c r="M60">
-        <v>49.43313378</v>
+        <v>50.28542919</v>
       </c>
       <c r="N60">
-        <v>77.36686621999999</v>
+        <v>76.51457081000001</v>
       </c>
       <c r="O60">
-        <v>11.605029933</v>
+        <v>11.4771856215</v>
       </c>
       <c r="P60">
-        <v>65.76183628699999</v>
+        <v>65.03738518850001</v>
       </c>
       <c r="Q60">
-        <v>76.66183628699999</v>
+        <v>75.9373851885</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1319447786794443</v>
+        <v>0.1339008885791992</v>
       </c>
       <c r="T60">
-        <v>1.634134619083957</v>
+        <v>1.671241301054981</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.565081157191406</v>
+        <v>2.521605205374603</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0909572143174717</v>
+        <v>0.09303992158957679</v>
       </c>
       <c r="C61">
-        <v>438.2581323108404</v>
+        <v>409.6409804818097</v>
       </c>
       <c r="D61">
-        <v>905.8382323108402</v>
+        <v>889.0749804818096</v>
       </c>
       <c r="E61">
-        <v>697.5900999999999</v>
+        <v>709.444</v>
       </c>
       <c r="F61">
-        <v>699.3800999999999</v>
+        <v>711.2339999999999</v>
       </c>
       <c r="G61">
         <v>231.8</v>
@@ -6289,45 +6289,45 @@
         <v>126.8</v>
       </c>
       <c r="M61">
-        <v>50.28542919</v>
+        <v>53.9115372</v>
       </c>
       <c r="N61">
-        <v>76.51457081000001</v>
+        <v>72.8884628</v>
       </c>
       <c r="O61">
-        <v>11.4771856215</v>
+        <v>10.93326942</v>
       </c>
       <c r="P61">
-        <v>65.03738518850001</v>
+        <v>61.95519338</v>
       </c>
       <c r="Q61">
-        <v>75.9373851885</v>
+        <v>72.85519337999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1339008885791992</v>
+        <v>0.135954803973942</v>
       </c>
       <c r="T61">
-        <v>1.671241301054981</v>
+        <v>1.710203317124557</v>
       </c>
       <c r="U61">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.15</v>
       </c>
       <c r="W61">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.521605205374603</v>
+        <v>2.352001196508268</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09303992158957679</v>
+        <v>0.09316677886168187</v>
       </c>
       <c r="C62">
-        <v>409.6409804818097</v>
+        <v>396.7860578597355</v>
       </c>
       <c r="D62">
-        <v>889.0749804818096</v>
+        <v>888.0739578597354</v>
       </c>
       <c r="E62">
-        <v>709.444</v>
+        <v>721.2978999999999</v>
       </c>
       <c r="F62">
-        <v>711.2339999999999</v>
+        <v>723.0878999999999</v>
       </c>
       <c r="G62">
         <v>231.8</v>
@@ -6371,28 +6371,28 @@
         <v>126.8</v>
       </c>
       <c r="M62">
-        <v>53.9115372</v>
+        <v>54.81006281999999</v>
       </c>
       <c r="N62">
-        <v>72.8884628</v>
+        <v>71.98993718</v>
       </c>
       <c r="O62">
-        <v>10.93326942</v>
+        <v>10.798490577</v>
       </c>
       <c r="P62">
-        <v>61.95519338</v>
+        <v>61.191446603</v>
       </c>
       <c r="Q62">
-        <v>72.85519337999999</v>
+        <v>72.09144660299999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.135954803973942</v>
+        <v>0.1381140483632869</v>
       </c>
       <c r="T62">
-        <v>1.710203317124557</v>
+        <v>1.751163385300265</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.352001196508268</v>
+        <v>2.313443799844198</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09316677886168187</v>
+        <v>0.09329363613378697</v>
       </c>
       <c r="C63">
-        <v>396.7860578597355</v>
+        <v>383.9333868347977</v>
       </c>
       <c r="D63">
-        <v>888.0739578597354</v>
+        <v>887.0751868347977</v>
       </c>
       <c r="E63">
-        <v>721.2978999999999</v>
+        <v>733.1518</v>
       </c>
       <c r="F63">
-        <v>723.0878999999999</v>
+        <v>734.9417999999999</v>
       </c>
       <c r="G63">
         <v>231.8</v>
@@ -6453,28 +6453,28 @@
         <v>126.8</v>
       </c>
       <c r="M63">
-        <v>54.81006281999999</v>
+        <v>55.70858844</v>
       </c>
       <c r="N63">
-        <v>71.98993718</v>
+        <v>71.09141156</v>
       </c>
       <c r="O63">
-        <v>10.798490577</v>
+        <v>10.663711734</v>
       </c>
       <c r="P63">
-        <v>61.191446603</v>
+        <v>60.42769982599999</v>
       </c>
       <c r="Q63">
-        <v>72.09144660299999</v>
+        <v>71.32769982599999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1381140483632869</v>
+        <v>0.1403869371941762</v>
       </c>
       <c r="T63">
-        <v>1.751163385300265</v>
+        <v>1.794279246537852</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.313443799844198</v>
+        <v>2.276130190169292</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09329363613378697</v>
+        <v>0.09342049340589206</v>
       </c>
       <c r="C64">
-        <v>383.9333868347977</v>
+        <v>371.0829598187645</v>
       </c>
       <c r="D64">
-        <v>887.0751868347977</v>
+        <v>886.0786598187644</v>
       </c>
       <c r="E64">
-        <v>733.1518</v>
+        <v>745.0056999999999</v>
       </c>
       <c r="F64">
-        <v>734.9417999999999</v>
+        <v>746.7956999999999</v>
       </c>
       <c r="G64">
         <v>231.8</v>
@@ -6535,28 +6535,28 @@
         <v>126.8</v>
       </c>
       <c r="M64">
-        <v>55.70858844</v>
+        <v>56.60711405999999</v>
       </c>
       <c r="N64">
-        <v>71.09141156</v>
+        <v>70.19288594</v>
       </c>
       <c r="O64">
-        <v>10.663711734</v>
+        <v>10.528932891</v>
       </c>
       <c r="P64">
-        <v>60.42769982599999</v>
+        <v>59.663953049</v>
       </c>
       <c r="Q64">
-        <v>71.32769982599999</v>
+        <v>70.56395304899999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1403869371941762</v>
+        <v>0.1427826848807894</v>
       </c>
       <c r="T64">
-        <v>1.794279246537852</v>
+        <v>1.839725694869363</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.276130190169292</v>
+        <v>2.240001139531684</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09342049340589206</v>
+        <v>0.09354735067799716</v>
       </c>
       <c r="C65">
-        <v>371.0829598187645</v>
+        <v>358.2347692574642</v>
       </c>
       <c r="D65">
-        <v>886.0786598187644</v>
+        <v>885.0843692574641</v>
       </c>
       <c r="E65">
-        <v>745.0056999999999</v>
+        <v>756.8596</v>
       </c>
       <c r="F65">
-        <v>746.7956999999999</v>
+        <v>758.6496</v>
       </c>
       <c r="G65">
         <v>231.8</v>
@@ -6617,28 +6617,28 @@
         <v>126.8</v>
       </c>
       <c r="M65">
-        <v>56.60711405999999</v>
+        <v>57.50563968</v>
       </c>
       <c r="N65">
-        <v>70.19288594</v>
+        <v>69.29436032</v>
       </c>
       <c r="O65">
-        <v>10.528932891</v>
+        <v>10.394154048</v>
       </c>
       <c r="P65">
-        <v>59.663953049</v>
+        <v>58.900206272</v>
       </c>
       <c r="Q65">
-        <v>70.56395304899999</v>
+        <v>69.800206272</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1427826848807894</v>
+        <v>0.1453115296611032</v>
       </c>
       <c r="T65">
-        <v>1.839725694869363</v>
+        <v>1.887696945885958</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.240001139531684</v>
+        <v>2.205001121726501</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09354735067799716</v>
+        <v>0.09367420795010226</v>
       </c>
       <c r="C66">
-        <v>358.2347692574642</v>
+        <v>345.3888076305931</v>
       </c>
       <c r="D66">
-        <v>885.0843692574641</v>
+        <v>884.092307630593</v>
       </c>
       <c r="E66">
-        <v>756.8596</v>
+        <v>768.7135</v>
       </c>
       <c r="F66">
-        <v>758.6496</v>
+        <v>770.5034999999999</v>
       </c>
       <c r="G66">
         <v>231.8</v>
@@ -6699,28 +6699,28 @@
         <v>126.8</v>
       </c>
       <c r="M66">
-        <v>57.50563968</v>
+        <v>58.4041653</v>
       </c>
       <c r="N66">
-        <v>69.29436032</v>
+        <v>68.39583469999999</v>
       </c>
       <c r="O66">
-        <v>10.394154048</v>
+        <v>10.259375205</v>
       </c>
       <c r="P66">
-        <v>58.900206272</v>
+        <v>58.136459495</v>
       </c>
       <c r="Q66">
-        <v>69.800206272</v>
+        <v>69.03645949499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1453115296611032</v>
+        <v>0.147984879857435</v>
       </c>
       <c r="T66">
-        <v>1.887696945885958</v>
+        <v>1.938409411246358</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.205001121726501</v>
+        <v>2.171078027546093</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09367420795010226</v>
+        <v>0.09380106522220735</v>
       </c>
       <c r="C67">
-        <v>345.3888076305931</v>
+        <v>332.5450674515279</v>
       </c>
       <c r="D67">
-        <v>884.092307630593</v>
+        <v>883.1024674515278</v>
       </c>
       <c r="E67">
-        <v>768.7135</v>
+        <v>780.5674</v>
       </c>
       <c r="F67">
-        <v>770.5034999999999</v>
+        <v>782.3574</v>
       </c>
       <c r="G67">
         <v>231.8</v>
@@ -6781,28 +6781,28 @@
         <v>126.8</v>
       </c>
       <c r="M67">
-        <v>58.4041653</v>
+        <v>59.30269092</v>
       </c>
       <c r="N67">
-        <v>68.39583469999999</v>
+        <v>67.49730907999999</v>
       </c>
       <c r="O67">
-        <v>10.259375205</v>
+        <v>10.124596362</v>
       </c>
       <c r="P67">
-        <v>58.136459495</v>
+        <v>57.372712718</v>
       </c>
       <c r="Q67">
-        <v>69.03645949499999</v>
+        <v>68.27271271799998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.147984879857435</v>
+        <v>0.1508154859476687</v>
       </c>
       <c r="T67">
-        <v>1.938409411246358</v>
+        <v>1.992104962804429</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.171078027546093</v>
+        <v>2.138182905916607</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09380106522220735</v>
+        <v>0.09392792249431244</v>
       </c>
       <c r="C68">
-        <v>332.5450674515279</v>
+        <v>319.7035412671353</v>
       </c>
       <c r="D68">
-        <v>883.1024674515278</v>
+        <v>882.1148412671353</v>
       </c>
       <c r="E68">
-        <v>780.5674</v>
+        <v>792.4213</v>
       </c>
       <c r="F68">
-        <v>782.3574</v>
+        <v>794.2112999999999</v>
       </c>
       <c r="G68">
         <v>231.8</v>
@@ -6863,28 +6863,28 @@
         <v>126.8</v>
       </c>
       <c r="M68">
-        <v>59.30269092</v>
+        <v>60.20121654</v>
       </c>
       <c r="N68">
-        <v>67.49730907999999</v>
+        <v>66.59878345999999</v>
       </c>
       <c r="O68">
-        <v>10.124596362</v>
+        <v>9.989817518999999</v>
       </c>
       <c r="P68">
-        <v>57.372712718</v>
+        <v>56.60896594099999</v>
       </c>
       <c r="Q68">
-        <v>68.27271271799998</v>
+        <v>67.50896594099999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1508154859476687</v>
+        <v>0.1538176439221589</v>
       </c>
       <c r="T68">
-        <v>1.992104962804429</v>
+        <v>2.049054790214504</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.138182905916607</v>
+        <v>2.106269728216359</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09392792249431244</v>
+        <v>0.09405477976641753</v>
       </c>
       <c r="C69">
-        <v>319.7035412671353</v>
+        <v>306.8642216575863</v>
       </c>
       <c r="D69">
-        <v>882.1148412671353</v>
+        <v>881.1294216575864</v>
       </c>
       <c r="E69">
-        <v>792.4213</v>
+        <v>804.2752</v>
       </c>
       <c r="F69">
-        <v>794.2112999999999</v>
+        <v>806.0652</v>
       </c>
       <c r="G69">
         <v>231.8</v>
@@ -6945,28 +6945,28 @@
         <v>126.8</v>
       </c>
       <c r="M69">
-        <v>60.20121654</v>
+        <v>61.09974216000001</v>
       </c>
       <c r="N69">
-        <v>66.59878345999999</v>
+        <v>65.70025783999999</v>
       </c>
       <c r="O69">
-        <v>9.989817518999999</v>
+        <v>9.855038675999998</v>
       </c>
       <c r="P69">
-        <v>56.60896594099999</v>
+        <v>55.84521916399999</v>
       </c>
       <c r="Q69">
-        <v>67.50896594099999</v>
+        <v>66.74521916399999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1538176439221589</v>
+        <v>0.1570074367700548</v>
       </c>
       <c r="T69">
-        <v>2.049054790214504</v>
+        <v>2.109563981837709</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.106269728216359</v>
+        <v>2.075295173389648</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09405477976641753</v>
+        <v>0.09418163703852264</v>
       </c>
       <c r="C70">
-        <v>306.8642216575863</v>
+        <v>294.0271012361703</v>
       </c>
       <c r="D70">
-        <v>881.1294216575864</v>
+        <v>880.1462012361702</v>
       </c>
       <c r="E70">
-        <v>804.2752</v>
+        <v>816.1291</v>
       </c>
       <c r="F70">
-        <v>806.0652</v>
+        <v>817.9191</v>
       </c>
       <c r="G70">
         <v>231.8</v>
@@ -7027,28 +7027,28 @@
         <v>126.8</v>
       </c>
       <c r="M70">
-        <v>61.09974216000001</v>
+        <v>61.99826778</v>
       </c>
       <c r="N70">
-        <v>65.70025783999999</v>
+        <v>64.80173221999999</v>
       </c>
       <c r="O70">
-        <v>9.855038675999998</v>
+        <v>9.720259832999998</v>
       </c>
       <c r="P70">
-        <v>55.84521916399999</v>
+        <v>55.08147238699999</v>
       </c>
       <c r="Q70">
-        <v>66.74521916399999</v>
+        <v>65.98147238699998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1570074367700548</v>
+        <v>0.1604030227049117</v>
       </c>
       <c r="T70">
-        <v>2.109563981837709</v>
+        <v>2.173976992275315</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.075295173389648</v>
+        <v>2.04521843174632</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09418163703852264</v>
+        <v>0.09430849431062771</v>
       </c>
       <c r="C71">
-        <v>294.0271012361703</v>
+        <v>281.1921726491097</v>
       </c>
       <c r="D71">
-        <v>880.1462012361702</v>
+        <v>879.1651726491096</v>
       </c>
       <c r="E71">
-        <v>816.1291</v>
+        <v>827.9830000000001</v>
       </c>
       <c r="F71">
-        <v>817.9191</v>
+        <v>829.773</v>
       </c>
       <c r="G71">
         <v>231.8</v>
@@ -7109,28 +7109,28 @@
         <v>126.8</v>
       </c>
       <c r="M71">
-        <v>61.99826778</v>
+        <v>62.89679340000001</v>
       </c>
       <c r="N71">
-        <v>64.80173221999999</v>
+        <v>63.90320659999999</v>
       </c>
       <c r="O71">
-        <v>9.720259832999998</v>
+        <v>9.585480989999999</v>
       </c>
       <c r="P71">
-        <v>55.08147238699999</v>
+        <v>54.31772560999999</v>
       </c>
       <c r="Q71">
-        <v>65.98147238699998</v>
+        <v>65.21772560999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1604030227049117</v>
+        <v>0.1640249810354258</v>
       </c>
       <c r="T71">
-        <v>2.173976992275315</v>
+        <v>2.24268420340876</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.04521843174632</v>
+        <v>2.016001025578515</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09430849431062771</v>
+        <v>0.1030050515827328</v>
       </c>
       <c r="C72">
-        <v>281.1921726491097</v>
+        <v>206.9287334773012</v>
       </c>
       <c r="D72">
-        <v>879.1651726491096</v>
+        <v>816.7556334773012</v>
       </c>
       <c r="E72">
-        <v>827.9830000000001</v>
+        <v>839.8369</v>
       </c>
       <c r="F72">
-        <v>829.773</v>
+        <v>841.6269</v>
       </c>
       <c r="G72">
         <v>231.8</v>
@@ -7191,45 +7191,45 @@
         <v>126.8</v>
       </c>
       <c r="M72">
-        <v>62.89679340000001</v>
+        <v>75.746421</v>
       </c>
       <c r="N72">
-        <v>63.90320659999999</v>
+        <v>51.053579</v>
       </c>
       <c r="O72">
-        <v>9.585480989999999</v>
+        <v>7.658036849999999</v>
       </c>
       <c r="P72">
-        <v>54.31772560999999</v>
+        <v>43.39554215</v>
       </c>
       <c r="Q72">
-        <v>65.21772560999997</v>
+        <v>54.29554214999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1640249810354258</v>
+        <v>0.1678967295956304</v>
       </c>
       <c r="T72">
-        <v>2.24268420340876</v>
+        <v>2.316129842896237</v>
       </c>
       <c r="U72">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V72">
         <v>0.15</v>
       </c>
       <c r="W72">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.016001025578515</v>
+        <v>1.674006485402129</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1030050515827328</v>
+        <v>0.1032526088548379</v>
       </c>
       <c r="C73">
-        <v>206.9287334773013</v>
+        <v>193.427717202232</v>
       </c>
       <c r="D73">
-        <v>816.7556334773012</v>
+        <v>815.1085172022318</v>
       </c>
       <c r="E73">
-        <v>839.8368999999999</v>
+        <v>851.6908</v>
       </c>
       <c r="F73">
-        <v>841.6268999999999</v>
+        <v>853.4807999999999</v>
       </c>
       <c r="G73">
         <v>231.8</v>
@@ -7273,28 +7273,28 @@
         <v>126.8</v>
       </c>
       <c r="M73">
-        <v>75.74642099999998</v>
+        <v>76.813272</v>
       </c>
       <c r="N73">
-        <v>51.05357900000001</v>
+        <v>49.986728</v>
       </c>
       <c r="O73">
-        <v>7.658036850000002</v>
+        <v>7.498009199999999</v>
       </c>
       <c r="P73">
-        <v>43.39554215000001</v>
+        <v>42.4887188</v>
       </c>
       <c r="Q73">
-        <v>54.29554215</v>
+        <v>53.38871879999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1678967295956304</v>
+        <v>0.1720450316244211</v>
       </c>
       <c r="T73">
-        <v>2.316129842896236</v>
+        <v>2.394821599489961</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.674006485402129</v>
+        <v>1.650756395327099</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1032526088548379</v>
+        <v>0.103500166126943</v>
       </c>
       <c r="C74">
-        <v>193.427717202232</v>
+        <v>179.9333308951691</v>
       </c>
       <c r="D74">
-        <v>815.1085172022318</v>
+        <v>813.4680308951689</v>
       </c>
       <c r="E74">
-        <v>851.6908</v>
+        <v>863.5446999999999</v>
       </c>
       <c r="F74">
-        <v>853.4807999999999</v>
+        <v>865.3346999999999</v>
       </c>
       <c r="G74">
         <v>231.8</v>
@@ -7355,28 +7355,28 @@
         <v>126.8</v>
       </c>
       <c r="M74">
-        <v>76.813272</v>
+        <v>77.88012299999998</v>
       </c>
       <c r="N74">
-        <v>49.986728</v>
+        <v>48.91987700000001</v>
       </c>
       <c r="O74">
-        <v>7.498009199999999</v>
+        <v>7.337981550000002</v>
       </c>
       <c r="P74">
-        <v>42.4887188</v>
+        <v>41.58189545000001</v>
       </c>
       <c r="Q74">
-        <v>53.38871879999999</v>
+        <v>52.48189545</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1720450316244211</v>
+        <v>0.1765006152849741</v>
       </c>
       <c r="T74">
-        <v>2.394821599489961</v>
+        <v>2.479342375090627</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.650756395327099</v>
+        <v>1.628143294021249</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.103500166126943</v>
+        <v>0.1037477233990481</v>
       </c>
       <c r="C75">
-        <v>179.9333308951691</v>
+        <v>166.4455346061218</v>
       </c>
       <c r="D75">
-        <v>813.4680308951689</v>
+        <v>811.8341346061217</v>
       </c>
       <c r="E75">
-        <v>863.5446999999999</v>
+        <v>875.3986</v>
       </c>
       <c r="F75">
-        <v>865.3346999999999</v>
+        <v>877.1886</v>
       </c>
       <c r="G75">
         <v>231.8</v>
@@ -7437,28 +7437,28 @@
         <v>126.8</v>
       </c>
       <c r="M75">
-        <v>77.88012299999998</v>
+        <v>78.946974</v>
       </c>
       <c r="N75">
-        <v>48.91987700000001</v>
+        <v>47.853026</v>
       </c>
       <c r="O75">
-        <v>7.337981550000002</v>
+        <v>7.177953899999999</v>
       </c>
       <c r="P75">
-        <v>41.58189545000001</v>
+        <v>40.6750721</v>
       </c>
       <c r="Q75">
-        <v>52.48189545</v>
+        <v>51.57507209999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1765006152849741</v>
+        <v>0.181298936150185</v>
       </c>
       <c r="T75">
-        <v>2.479342375090627</v>
+        <v>2.570364748814423</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.628143294021249</v>
+        <v>1.606141357615556</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1037477233990481</v>
+        <v>0.1039952806711532</v>
       </c>
       <c r="C76">
-        <v>166.4455346061218</v>
+        <v>152.964288705423</v>
       </c>
       <c r="D76">
-        <v>811.8341346061217</v>
+        <v>810.2067887054228</v>
       </c>
       <c r="E76">
-        <v>875.3986</v>
+        <v>887.2524999999999</v>
       </c>
       <c r="F76">
-        <v>877.1886</v>
+        <v>889.0424999999999</v>
       </c>
       <c r="G76">
         <v>231.8</v>
@@ -7519,28 +7519,28 @@
         <v>126.8</v>
       </c>
       <c r="M76">
-        <v>78.946974</v>
+        <v>80.01382499999998</v>
       </c>
       <c r="N76">
-        <v>47.853026</v>
+        <v>46.78617500000001</v>
       </c>
       <c r="O76">
-        <v>7.177953899999999</v>
+        <v>7.017926250000002</v>
       </c>
       <c r="P76">
-        <v>40.6750721</v>
+        <v>39.76824875000001</v>
       </c>
       <c r="Q76">
-        <v>51.57507209999999</v>
+        <v>50.66824875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.181298936150185</v>
+        <v>0.1864811226846128</v>
       </c>
       <c r="T76">
-        <v>2.570364748814423</v>
+        <v>2.668668912436122</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.606141357615556</v>
+        <v>1.584726139514016</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1039952806711532</v>
+        <v>0.1042428379432583</v>
       </c>
       <c r="C77">
-        <v>152.964288705423</v>
+        <v>139.4895538805254</v>
       </c>
       <c r="D77">
-        <v>810.2067887054228</v>
+        <v>808.5859538805252</v>
       </c>
       <c r="E77">
-        <v>887.2524999999999</v>
+        <v>899.1063999999999</v>
       </c>
       <c r="F77">
-        <v>889.0424999999999</v>
+        <v>900.8963999999999</v>
       </c>
       <c r="G77">
         <v>231.8</v>
@@ -7601,28 +7601,28 @@
         <v>126.8</v>
       </c>
       <c r="M77">
-        <v>80.01382499999998</v>
+        <v>81.08067599999998</v>
       </c>
       <c r="N77">
-        <v>46.78617500000001</v>
+        <v>45.71932400000001</v>
       </c>
       <c r="O77">
-        <v>7.017926250000002</v>
+        <v>6.857898600000002</v>
       </c>
       <c r="P77">
-        <v>39.76824875000001</v>
+        <v>38.86142540000002</v>
       </c>
       <c r="Q77">
-        <v>50.66824875</v>
+        <v>49.76142540000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1864811226846128</v>
+        <v>0.1920951580969095</v>
       </c>
       <c r="T77">
-        <v>2.668668912436122</v>
+        <v>2.775165089692963</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.584726139514016</v>
+        <v>1.563874479783568</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1042428379432583</v>
+        <v>0.1044903952153634</v>
       </c>
       <c r="C78">
-        <v>139.4895538805254</v>
+        <v>126.021291132836</v>
       </c>
       <c r="D78">
-        <v>808.5859538805252</v>
+        <v>806.971591132836</v>
       </c>
       <c r="E78">
-        <v>899.1063999999999</v>
+        <v>910.9603</v>
       </c>
       <c r="F78">
-        <v>900.8963999999999</v>
+        <v>912.7502999999999</v>
       </c>
       <c r="G78">
         <v>231.8</v>
@@ -7683,28 +7683,28 @@
         <v>126.8</v>
       </c>
       <c r="M78">
-        <v>81.08067599999998</v>
+        <v>82.147527</v>
       </c>
       <c r="N78">
-        <v>45.71932400000001</v>
+        <v>44.652473</v>
       </c>
       <c r="O78">
-        <v>6.857898600000002</v>
+        <v>6.69787095</v>
       </c>
       <c r="P78">
-        <v>38.86142540000002</v>
+        <v>37.95460205</v>
       </c>
       <c r="Q78">
-        <v>49.76142540000001</v>
+        <v>48.85460204999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1920951580969095</v>
+        <v>0.1981973705015799</v>
       </c>
       <c r="T78">
-        <v>2.775165089692963</v>
+        <v>2.890921804102572</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.563874479783568</v>
+        <v>1.54356442160456</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1044903952153634</v>
+        <v>0.1047379524874685</v>
       </c>
       <c r="C79">
-        <v>126.021291132836</v>
+        <v>112.5594617745879</v>
       </c>
       <c r="D79">
-        <v>806.971591132836</v>
+        <v>805.3636617745877</v>
       </c>
       <c r="E79">
-        <v>910.9603</v>
+        <v>922.8141999999999</v>
       </c>
       <c r="F79">
-        <v>912.7502999999999</v>
+        <v>924.6041999999999</v>
       </c>
       <c r="G79">
         <v>231.8</v>
@@ -7765,28 +7765,28 @@
         <v>126.8</v>
       </c>
       <c r="M79">
-        <v>82.147527</v>
+        <v>83.21437799999998</v>
       </c>
       <c r="N79">
-        <v>44.652473</v>
+        <v>43.58562200000001</v>
       </c>
       <c r="O79">
-        <v>6.69787095</v>
+        <v>6.537843300000002</v>
       </c>
       <c r="P79">
-        <v>37.95460205</v>
+        <v>37.04777870000001</v>
       </c>
       <c r="Q79">
-        <v>48.85460204999999</v>
+        <v>47.9477787</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1981973705015799</v>
+        <v>0.2048543294884931</v>
       </c>
       <c r="T79">
-        <v>2.890921804102572</v>
+        <v>3.017201856185782</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.54356442160456</v>
+        <v>1.523775134148092</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1047379524874685</v>
+        <v>0.1049855097595736</v>
       </c>
       <c r="C80">
-        <v>112.5594617745879</v>
+        <v>99.10402742574968</v>
       </c>
       <c r="D80">
-        <v>805.3636617745877</v>
+        <v>803.7621274257496</v>
       </c>
       <c r="E80">
-        <v>922.8141999999999</v>
+        <v>934.6681</v>
       </c>
       <c r="F80">
-        <v>924.6041999999999</v>
+        <v>936.4580999999999</v>
       </c>
       <c r="G80">
         <v>231.8</v>
@@ -7847,28 +7847,28 @@
         <v>126.8</v>
       </c>
       <c r="M80">
-        <v>83.21437799999998</v>
+        <v>84.281229</v>
       </c>
       <c r="N80">
-        <v>43.58562200000001</v>
+        <v>42.518771</v>
       </c>
       <c r="O80">
-        <v>6.537843300000002</v>
+        <v>6.37781565</v>
       </c>
       <c r="P80">
-        <v>37.04777870000001</v>
+        <v>36.14095535</v>
       </c>
       <c r="Q80">
-        <v>47.9477787</v>
+        <v>47.04095534999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2048543294884931</v>
+        <v>0.2121452845693979</v>
       </c>
       <c r="T80">
-        <v>3.017201856185782</v>
+        <v>3.155508579895965</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.523775134148092</v>
+        <v>1.504486841310774</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1049855097595736</v>
+        <v>0.1458517093832615</v>
       </c>
       <c r="C81">
-        <v>99.10402742574968</v>
+        <v>-111.3930125375728</v>
       </c>
       <c r="D81">
-        <v>803.7621274257496</v>
+        <v>605.1189874624272</v>
       </c>
       <c r="E81">
-        <v>934.6681</v>
+        <v>946.5219999999999</v>
       </c>
       <c r="F81">
-        <v>936.4580999999999</v>
+        <v>948.3119999999999</v>
       </c>
       <c r="G81">
         <v>231.8</v>
@@ -7929,45 +7929,45 @@
         <v>126.8</v>
       </c>
       <c r="M81">
-        <v>84.281229</v>
+        <v>139.2122016</v>
       </c>
       <c r="N81">
-        <v>42.518771</v>
+        <v>-12.41220159999999</v>
       </c>
       <c r="O81">
-        <v>6.37781565</v>
+        <v>-1.861830239999998</v>
       </c>
       <c r="P81">
-        <v>36.14095535</v>
+        <v>-10.55037135999999</v>
       </c>
       <c r="Q81">
-        <v>47.04095534999999</v>
+        <v>0.3496286400000006</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2121452845693979</v>
+        <v>0.2222853077292043</v>
       </c>
       <c r="T81">
-        <v>3.155508579895965</v>
+        <v>3.347861072267121</v>
       </c>
       <c r="U81">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.15</v>
+        <v>0.1366259550628355</v>
       </c>
       <c r="W81">
-        <v>0.0765</v>
+        <v>0.1267433097967758</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.504486841310774</v>
+        <v>0.9108397004189036</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1458517093832615</v>
+        <v>0.1468617093832614</v>
       </c>
       <c r="C82">
-        <v>-111.3930125375728</v>
+        <v>-126.9205754814097</v>
       </c>
       <c r="D82">
-        <v>605.1189874624272</v>
+        <v>601.4453245185902</v>
       </c>
       <c r="E82">
-        <v>946.5219999999999</v>
+        <v>958.3759</v>
       </c>
       <c r="F82">
-        <v>948.3119999999999</v>
+        <v>960.1659</v>
       </c>
       <c r="G82">
         <v>231.8</v>
@@ -8011,37 +8011,37 @@
         <v>126.8</v>
       </c>
       <c r="M82">
-        <v>139.2122016</v>
+        <v>140.95235412</v>
       </c>
       <c r="N82">
-        <v>-12.41220159999999</v>
+        <v>-14.15235412</v>
       </c>
       <c r="O82">
-        <v>-1.861830239999998</v>
+        <v>-2.122853118</v>
       </c>
       <c r="P82">
-        <v>-10.55037135999999</v>
+        <v>-12.029501002</v>
       </c>
       <c r="Q82">
-        <v>0.3496286400000006</v>
+        <v>-1.129501002000007</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2222853077292043</v>
+        <v>0.2315740081360045</v>
       </c>
       <c r="T82">
-        <v>3.347861072267121</v>
+        <v>3.524064286596969</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1366259550628355</v>
+        <v>0.1349392148768746</v>
       </c>
       <c r="W82">
-        <v>0.1267433097967758</v>
+        <v>0.1269909232560748</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9108397004189036</v>
+        <v>0.8995947658458306</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1468617093832614</v>
+        <v>0.1478717093832615</v>
       </c>
       <c r="C83">
-        <v>-126.9205754814097</v>
+        <v>-142.4038021494529</v>
       </c>
       <c r="D83">
-        <v>601.4453245185902</v>
+        <v>597.815997850547</v>
       </c>
       <c r="E83">
-        <v>958.3759</v>
+        <v>970.2298</v>
       </c>
       <c r="F83">
-        <v>960.1659</v>
+        <v>972.0197999999999</v>
       </c>
       <c r="G83">
         <v>231.8</v>
@@ -8093,37 +8093,37 @@
         <v>126.8</v>
       </c>
       <c r="M83">
-        <v>140.95235412</v>
+        <v>142.69250664</v>
       </c>
       <c r="N83">
-        <v>-14.15235412</v>
+        <v>-15.89250664000001</v>
       </c>
       <c r="O83">
-        <v>-2.122853118</v>
+        <v>-2.383875996000001</v>
       </c>
       <c r="P83">
-        <v>-12.029501002</v>
+        <v>-13.50863064400001</v>
       </c>
       <c r="Q83">
-        <v>-1.129501002000007</v>
+        <v>-2.608630644000016</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2315740081360045</v>
+        <v>0.2418947863657826</v>
       </c>
       <c r="T83">
-        <v>3.524064286596969</v>
+        <v>3.719845635852356</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1349392148768746</v>
+        <v>0.1332936146954493</v>
       </c>
       <c r="W83">
-        <v>0.1269909232560748</v>
+        <v>0.1272324973627081</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8995947658458306</v>
+        <v>0.8886240979696619</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1478717093832615</v>
+        <v>0.1488817093832615</v>
       </c>
       <c r="C84">
-        <v>-142.4038021494529</v>
+        <v>-157.8434903481931</v>
       </c>
       <c r="D84">
-        <v>597.815997850547</v>
+        <v>594.2302096518069</v>
       </c>
       <c r="E84">
-        <v>970.2298</v>
+        <v>982.0837</v>
       </c>
       <c r="F84">
-        <v>972.0197999999999</v>
+        <v>983.8737</v>
       </c>
       <c r="G84">
         <v>231.8</v>
@@ -8175,37 +8175,37 @@
         <v>126.8</v>
       </c>
       <c r="M84">
-        <v>142.69250664</v>
+        <v>144.43265916</v>
       </c>
       <c r="N84">
-        <v>-15.89250664000001</v>
+        <v>-17.63265916000002</v>
       </c>
       <c r="O84">
-        <v>-2.383875996000001</v>
+        <v>-2.644898874000003</v>
       </c>
       <c r="P84">
-        <v>-13.50863064400001</v>
+        <v>-14.98776028600001</v>
       </c>
       <c r="Q84">
-        <v>-2.608630644000016</v>
+        <v>-4.087760286000023</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2418947863657826</v>
+        <v>0.2534297737990639</v>
       </c>
       <c r="T84">
-        <v>3.719845635852356</v>
+        <v>3.938660085020142</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1332936146954493</v>
+        <v>0.1316876675304439</v>
       </c>
       <c r="W84">
-        <v>0.1272324973627081</v>
+        <v>0.1274682504065308</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8886240979696619</v>
+        <v>0.8779177835362925</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1488817093832615</v>
+        <v>0.1498917093832615</v>
       </c>
       <c r="C85">
-        <v>-157.8434903481931</v>
+        <v>-173.2404188568075</v>
       </c>
       <c r="D85">
-        <v>594.2302096518069</v>
+        <v>590.6871811431924</v>
       </c>
       <c r="E85">
-        <v>982.0837</v>
+        <v>993.9376</v>
       </c>
       <c r="F85">
-        <v>983.8737</v>
+        <v>995.7275999999999</v>
       </c>
       <c r="G85">
         <v>231.8</v>
@@ -8257,37 +8257,37 @@
         <v>126.8</v>
       </c>
       <c r="M85">
-        <v>144.43265916</v>
+        <v>146.17281168</v>
       </c>
       <c r="N85">
-        <v>-17.63265916000002</v>
+        <v>-19.37281168</v>
       </c>
       <c r="O85">
-        <v>-2.644898874000003</v>
+        <v>-2.905921752</v>
       </c>
       <c r="P85">
-        <v>-14.98776028600001</v>
+        <v>-16.466889928</v>
       </c>
       <c r="Q85">
-        <v>-4.087760286000023</v>
+        <v>-5.566889928000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2534297737990639</v>
+        <v>0.2664066346615054</v>
       </c>
       <c r="T85">
-        <v>3.938660085020142</v>
+        <v>4.184826340333902</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1316876675304439</v>
+        <v>0.1301199572027005</v>
       </c>
       <c r="W85">
-        <v>0.1274682504065308</v>
+        <v>0.1276983902826436</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8779177835362925</v>
+        <v>0.8674663813513367</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1498917093832615</v>
+        <v>0.1509017093832614</v>
       </c>
       <c r="C86">
-        <v>-173.2404188568074</v>
+        <v>-188.5953479910387</v>
       </c>
       <c r="D86">
-        <v>590.6871811431924</v>
+        <v>587.1861520089612</v>
       </c>
       <c r="E86">
-        <v>993.9375999999999</v>
+        <v>1005.7915</v>
       </c>
       <c r="F86">
-        <v>995.7275999999998</v>
+        <v>1007.5815</v>
       </c>
       <c r="G86">
         <v>231.8</v>
@@ -8339,37 +8339,37 @@
         <v>126.8</v>
       </c>
       <c r="M86">
-        <v>146.17281168</v>
+        <v>147.9129642</v>
       </c>
       <c r="N86">
-        <v>-19.37281168</v>
+        <v>-21.11296420000001</v>
       </c>
       <c r="O86">
-        <v>-2.905921752</v>
+        <v>-3.166944630000001</v>
       </c>
       <c r="P86">
-        <v>-16.466889928</v>
+        <v>-17.94601957000001</v>
       </c>
       <c r="Q86">
-        <v>-5.566889928000005</v>
+        <v>-7.046019570000016</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2664066346615053</v>
+        <v>0.281113743638939</v>
       </c>
       <c r="T86">
-        <v>4.184826340333899</v>
+        <v>4.463814763022826</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1301199572027005</v>
+        <v>0.1285891341767864</v>
       </c>
       <c r="W86">
-        <v>0.1276983902826436</v>
+        <v>0.1279231151028478</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8674663813513367</v>
+        <v>0.8572608945119091</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1509017093832614</v>
+        <v>0.1519117093832614</v>
       </c>
       <c r="C87">
-        <v>-188.5953479910387</v>
+        <v>-203.9090201471381</v>
       </c>
       <c r="D87">
-        <v>587.1861520089612</v>
+        <v>583.7263798528617</v>
       </c>
       <c r="E87">
-        <v>1005.7915</v>
+        <v>1017.6454</v>
       </c>
       <c r="F87">
-        <v>1007.5815</v>
+        <v>1019.4354</v>
       </c>
       <c r="G87">
         <v>231.8</v>
@@ -8421,37 +8421,37 @@
         <v>126.8</v>
       </c>
       <c r="M87">
-        <v>147.9129642</v>
+        <v>149.65311672</v>
       </c>
       <c r="N87">
-        <v>-21.11296420000001</v>
+        <v>-22.85311671999999</v>
       </c>
       <c r="O87">
-        <v>-3.166944630000001</v>
+        <v>-3.427967507999998</v>
       </c>
       <c r="P87">
-        <v>-17.94601957000001</v>
+        <v>-19.42514921199999</v>
       </c>
       <c r="Q87">
-        <v>-7.046019570000016</v>
+        <v>-8.525149211999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.281113743638939</v>
+        <v>0.2979218681845775</v>
       </c>
       <c r="T87">
-        <v>4.463814763022826</v>
+        <v>4.782658674667314</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1285891341767864</v>
+        <v>0.1270939116863586</v>
       </c>
       <c r="W87">
-        <v>0.1279231151028478</v>
+        <v>0.1281426137644426</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8572608945119091</v>
+        <v>0.8472927445757242</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1519117093832614</v>
+        <v>0.1529217093832615</v>
       </c>
       <c r="C88">
-        <v>-203.9090201471381</v>
+        <v>-219.1821603266937</v>
       </c>
       <c r="D88">
-        <v>583.7263798528617</v>
+        <v>580.3071396733061</v>
       </c>
       <c r="E88">
-        <v>1017.6454</v>
+        <v>1029.4993</v>
       </c>
       <c r="F88">
-        <v>1019.4354</v>
+        <v>1031.2893</v>
       </c>
       <c r="G88">
         <v>231.8</v>
@@ -8503,37 +8503,37 @@
         <v>126.8</v>
       </c>
       <c r="M88">
-        <v>149.65311672</v>
+        <v>151.39326924</v>
       </c>
       <c r="N88">
-        <v>-22.85311671999999</v>
+        <v>-24.59326924</v>
       </c>
       <c r="O88">
-        <v>-3.427967507999998</v>
+        <v>-3.688990386</v>
       </c>
       <c r="P88">
-        <v>-19.42514921199999</v>
+        <v>-20.904278854</v>
       </c>
       <c r="Q88">
-        <v>-8.525149211999999</v>
+        <v>-10.00427885400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2979218681845775</v>
+        <v>0.3173158580449296</v>
       </c>
       <c r="T88">
-        <v>4.782658674667314</v>
+        <v>5.150555495795569</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1270939116863586</v>
+        <v>0.1256330621267453</v>
       </c>
       <c r="W88">
-        <v>0.1281426137644426</v>
+        <v>0.1283570664797938</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8472927445757242</v>
+        <v>0.8375537475116355</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1529217093832615</v>
+        <v>0.1539317093832615</v>
       </c>
       <c r="C89">
-        <v>-219.1821603266937</v>
+        <v>-234.4154766431168</v>
       </c>
       <c r="D89">
-        <v>580.3071396733061</v>
+        <v>576.9277233568831</v>
       </c>
       <c r="E89">
-        <v>1029.4993</v>
+        <v>1041.3532</v>
       </c>
       <c r="F89">
-        <v>1031.2893</v>
+        <v>1043.1432</v>
       </c>
       <c r="G89">
         <v>231.8</v>
@@ -8585,37 +8585,37 @@
         <v>126.8</v>
       </c>
       <c r="M89">
-        <v>151.39326924</v>
+        <v>153.13342176</v>
       </c>
       <c r="N89">
-        <v>-24.59326924</v>
+        <v>-26.33342176000001</v>
       </c>
       <c r="O89">
-        <v>-3.688990386</v>
+        <v>-3.950013264000001</v>
       </c>
       <c r="P89">
-        <v>-20.904278854</v>
+        <v>-22.38340849600001</v>
       </c>
       <c r="Q89">
-        <v>-10.00427885400001</v>
+        <v>-11.48340849600002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3173158580449296</v>
+        <v>0.3399421795486738</v>
       </c>
       <c r="T89">
-        <v>5.150555495795569</v>
+        <v>5.579768453778533</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1256330621267453</v>
+        <v>0.1242054136934868</v>
       </c>
       <c r="W89">
-        <v>0.1283570664797938</v>
+        <v>0.1285666452697961</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8375537475116355</v>
+        <v>0.8280360912899123</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1539317093832615</v>
+        <v>0.1549417093832615</v>
       </c>
       <c r="C90">
-        <v>-234.4154766431168</v>
+        <v>-249.6096608105377</v>
       </c>
       <c r="D90">
-        <v>576.9277233568831</v>
+        <v>573.5874391894621</v>
       </c>
       <c r="E90">
-        <v>1041.3532</v>
+        <v>1053.2071</v>
       </c>
       <c r="F90">
-        <v>1043.1432</v>
+        <v>1054.9971</v>
       </c>
       <c r="G90">
         <v>231.8</v>
@@ -8667,37 +8667,37 @@
         <v>126.8</v>
       </c>
       <c r="M90">
-        <v>153.13342176</v>
+        <v>154.87357428</v>
       </c>
       <c r="N90">
-        <v>-26.33342176000001</v>
+        <v>-28.07357427999999</v>
       </c>
       <c r="O90">
-        <v>-3.950013264000001</v>
+        <v>-4.211036141999998</v>
       </c>
       <c r="P90">
-        <v>-22.38340849600001</v>
+        <v>-23.86253813799999</v>
       </c>
       <c r="Q90">
-        <v>-11.48340849600002</v>
+        <v>-12.962538138</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3399421795486738</v>
+        <v>0.3666823776894624</v>
       </c>
       <c r="T90">
-        <v>5.579768453778533</v>
+        <v>6.087020131394765</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1242054136934868</v>
+        <v>0.1228098472474926</v>
       </c>
       <c r="W90">
-        <v>0.1285666452697961</v>
+        <v>0.1287715144240681</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8280360912899123</v>
+        <v>0.8187323149832841</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1549417093832615</v>
+        <v>0.1559517093832614</v>
       </c>
       <c r="C91">
-        <v>-249.6096608105377</v>
+        <v>-264.7653886158143</v>
       </c>
       <c r="D91">
-        <v>573.5874391894621</v>
+        <v>570.2856113841856</v>
       </c>
       <c r="E91">
-        <v>1053.2071</v>
+        <v>1065.061</v>
       </c>
       <c r="F91">
-        <v>1054.9971</v>
+        <v>1066.851</v>
       </c>
       <c r="G91">
         <v>231.8</v>
@@ -8749,37 +8749,37 @@
         <v>126.8</v>
       </c>
       <c r="M91">
-        <v>154.87357428</v>
+        <v>156.6137268</v>
       </c>
       <c r="N91">
-        <v>-28.07357427999999</v>
+        <v>-29.8137268</v>
       </c>
       <c r="O91">
-        <v>-4.211036141999998</v>
+        <v>-4.47205902</v>
       </c>
       <c r="P91">
-        <v>-23.86253813799999</v>
+        <v>-25.34166778</v>
       </c>
       <c r="Q91">
-        <v>-12.962538138</v>
+        <v>-14.44166778000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3666823776894624</v>
+        <v>0.3987706154584085</v>
       </c>
       <c r="T91">
-        <v>6.087020131394765</v>
+        <v>6.69572214453424</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1228098472474926</v>
+        <v>0.1214452933891871</v>
       </c>
       <c r="W91">
-        <v>0.1287715144240681</v>
+        <v>0.1289718309304673</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8187323149832841</v>
+        <v>0.8096352892612476</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1559517093832614</v>
+        <v>0.1569617093832615</v>
       </c>
       <c r="C92">
-        <v>-264.7653886158143</v>
+        <v>-279.8833203743295</v>
       </c>
       <c r="D92">
-        <v>570.2856113841856</v>
+        <v>567.0215796256704</v>
       </c>
       <c r="E92">
-        <v>1065.061</v>
+        <v>1076.9149</v>
       </c>
       <c r="F92">
-        <v>1066.851</v>
+        <v>1078.7049</v>
       </c>
       <c r="G92">
         <v>231.8</v>
@@ -8831,37 +8831,37 @@
         <v>126.8</v>
       </c>
       <c r="M92">
-        <v>156.6137268</v>
+        <v>158.35387932</v>
       </c>
       <c r="N92">
-        <v>-29.8137268</v>
+        <v>-31.55387932000001</v>
       </c>
       <c r="O92">
-        <v>-4.47205902</v>
+        <v>-4.733081898000001</v>
       </c>
       <c r="P92">
-        <v>-25.34166778</v>
+        <v>-26.82079742200001</v>
       </c>
       <c r="Q92">
-        <v>-14.44166778000001</v>
+        <v>-15.92079742200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3987706154584085</v>
+        <v>0.4379895727315651</v>
       </c>
       <c r="T92">
-        <v>6.69572214453424</v>
+        <v>7.439691271704713</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1214452933891871</v>
+        <v>0.1201107297255697</v>
       </c>
       <c r="W92">
-        <v>0.1289718309304673</v>
+        <v>0.1291677448762864</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8096352892612476</v>
+        <v>0.8007381981704645</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1569617093832615</v>
+        <v>0.2088165344865545</v>
       </c>
       <c r="C93">
-        <v>-279.8833203743295</v>
+        <v>-420.5160563828613</v>
       </c>
       <c r="D93">
-        <v>567.0215796256704</v>
+        <v>438.2427436171387</v>
       </c>
       <c r="E93">
-        <v>1076.9149</v>
+        <v>1088.7688</v>
       </c>
       <c r="F93">
-        <v>1078.7049</v>
+        <v>1090.5588</v>
       </c>
       <c r="G93">
         <v>231.8</v>
@@ -8913,45 +8913,45 @@
         <v>126.8</v>
       </c>
       <c r="M93">
-        <v>158.35387932</v>
+        <v>218.98420704</v>
       </c>
       <c r="N93">
-        <v>-31.55387932000001</v>
+        <v>-92.18420704</v>
       </c>
       <c r="O93">
-        <v>-4.733081898000001</v>
+        <v>-13.827631056</v>
       </c>
       <c r="P93">
-        <v>-26.82079742200001</v>
+        <v>-78.356575984</v>
       </c>
       <c r="Q93">
-        <v>-15.92079742200001</v>
+        <v>-67.45657598400001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4379895727315651</v>
+        <v>0.5015735831141737</v>
       </c>
       <c r="T93">
-        <v>7.439691271704713</v>
+        <v>8.645856452917348</v>
       </c>
       <c r="U93">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1201107297255697</v>
+        <v>0.08685557856930649</v>
       </c>
       <c r="W93">
-        <v>0.1291677448762864</v>
+        <v>0.1833593998232833</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8007381981704645</v>
+        <v>0.5790371904620433</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2088165344865545</v>
+        <v>0.2103665344865545</v>
       </c>
       <c r="C94">
-        <v>-420.5160563828613</v>
+        <v>-435.3249995404691</v>
       </c>
       <c r="D94">
-        <v>438.2427436171387</v>
+        <v>435.2877004595308</v>
       </c>
       <c r="E94">
-        <v>1088.7688</v>
+        <v>1100.6227</v>
       </c>
       <c r="F94">
-        <v>1090.5588</v>
+        <v>1102.4127</v>
       </c>
       <c r="G94">
         <v>231.8</v>
@@ -8995,37 +8995,37 @@
         <v>126.8</v>
       </c>
       <c r="M94">
-        <v>218.98420704</v>
+        <v>221.36447016</v>
       </c>
       <c r="N94">
-        <v>-92.18420704</v>
+        <v>-94.56447015999997</v>
       </c>
       <c r="O94">
-        <v>-13.827631056</v>
+        <v>-14.184670524</v>
       </c>
       <c r="P94">
-        <v>-78.356575984</v>
+        <v>-80.37979963599997</v>
       </c>
       <c r="Q94">
-        <v>-67.45657598400001</v>
+        <v>-69.47979963599998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5015735831141737</v>
+        <v>0.5666840949876271</v>
       </c>
       <c r="T94">
-        <v>8.645856452917348</v>
+        <v>9.880978803334113</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08685557856930649</v>
+        <v>0.08592164761694837</v>
       </c>
       <c r="W94">
-        <v>0.1833593998232833</v>
+        <v>0.1835469331585168</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5790371904620433</v>
+        <v>0.5728109841129891</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2103665344865545</v>
+        <v>0.2119165344865545</v>
       </c>
       <c r="C95">
-        <v>-435.3249995404691</v>
+        <v>-450.0943582743784</v>
       </c>
       <c r="D95">
-        <v>435.2877004595308</v>
+        <v>432.3722417256216</v>
       </c>
       <c r="E95">
-        <v>1100.6227</v>
+        <v>1112.4766</v>
       </c>
       <c r="F95">
-        <v>1102.4127</v>
+        <v>1114.2666</v>
       </c>
       <c r="G95">
         <v>231.8</v>
@@ -9077,37 +9077,37 @@
         <v>126.8</v>
       </c>
       <c r="M95">
-        <v>221.36447016</v>
+        <v>223.74473328</v>
       </c>
       <c r="N95">
-        <v>-94.56447015999997</v>
+        <v>-96.94473327999999</v>
       </c>
       <c r="O95">
-        <v>-14.184670524</v>
+        <v>-14.541709992</v>
       </c>
       <c r="P95">
-        <v>-80.37979963599997</v>
+        <v>-82.403023288</v>
       </c>
       <c r="Q95">
-        <v>-69.47979963599998</v>
+        <v>-71.50302328800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5666840949876271</v>
+        <v>0.6534981108188984</v>
       </c>
       <c r="T95">
-        <v>9.880978803334113</v>
+        <v>11.5278086038898</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08592164761694837</v>
+        <v>0.08500758753591699</v>
       </c>
       <c r="W95">
-        <v>0.1835469331585168</v>
+        <v>0.1837304764227879</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5728109841129891</v>
+        <v>0.5667172502394466</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2119165344865545</v>
+        <v>0.2134665344865545</v>
       </c>
       <c r="C96">
-        <v>-450.0943582743784</v>
+        <v>-464.824922675336</v>
       </c>
       <c r="D96">
-        <v>432.3722417256216</v>
+        <v>429.4955773246639</v>
       </c>
       <c r="E96">
-        <v>1112.4766</v>
+        <v>1124.3305</v>
       </c>
       <c r="F96">
-        <v>1114.2666</v>
+        <v>1126.1205</v>
       </c>
       <c r="G96">
         <v>231.8</v>
@@ -9159,37 +9159,37 @@
         <v>126.8</v>
       </c>
       <c r="M96">
-        <v>223.74473328</v>
+        <v>226.1249964</v>
       </c>
       <c r="N96">
-        <v>-96.94473327999999</v>
+        <v>-99.32499640000002</v>
       </c>
       <c r="O96">
-        <v>-14.541709992</v>
+        <v>-14.89874946</v>
       </c>
       <c r="P96">
-        <v>-82.403023288</v>
+        <v>-84.42624694000001</v>
       </c>
       <c r="Q96">
-        <v>-71.50302328800001</v>
+        <v>-73.52624694000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6534981108188984</v>
+        <v>0.7750377329826785</v>
       </c>
       <c r="T96">
-        <v>11.5278086038898</v>
+        <v>13.83337032466777</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08500758753591699</v>
+        <v>0.08411277082501259</v>
       </c>
       <c r="W96">
-        <v>0.1837304764227879</v>
+        <v>0.1839101556183375</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5667172502394466</v>
+        <v>0.560751805500084</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2134665344865545</v>
+        <v>0.2150165344865545</v>
       </c>
       <c r="C97">
-        <v>-464.824922675336</v>
+        <v>-479.5174619464917</v>
       </c>
       <c r="D97">
-        <v>429.4955773246639</v>
+        <v>426.6569380535083</v>
       </c>
       <c r="E97">
-        <v>1124.3305</v>
+        <v>1136.1844</v>
       </c>
       <c r="F97">
-        <v>1126.1205</v>
+        <v>1137.9744</v>
       </c>
       <c r="G97">
         <v>231.8</v>
@@ -9241,37 +9241,37 @@
         <v>126.8</v>
       </c>
       <c r="M97">
-        <v>226.1249964</v>
+        <v>228.50525952</v>
       </c>
       <c r="N97">
-        <v>-99.32499640000002</v>
+        <v>-101.70525952</v>
       </c>
       <c r="O97">
-        <v>-14.89874946</v>
+        <v>-15.255788928</v>
       </c>
       <c r="P97">
-        <v>-84.42624694000001</v>
+        <v>-86.44947059200001</v>
       </c>
       <c r="Q97">
-        <v>-73.52624694000002</v>
+        <v>-75.54947059200002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7750377329826785</v>
+        <v>0.9573471662283484</v>
       </c>
       <c r="T97">
-        <v>13.83337032466777</v>
+        <v>17.29171290583472</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08411277082501259</v>
+        <v>0.08323659612891871</v>
       </c>
       <c r="W97">
-        <v>0.1839101556183375</v>
+        <v>0.1840860914973131</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.560751805500084</v>
+        <v>0.5549106408594582</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2150165344865544</v>
+        <v>0.2165665344865545</v>
       </c>
       <c r="C98">
-        <v>-479.5174619464916</v>
+        <v>-494.1727250891229</v>
       </c>
       <c r="D98">
-        <v>426.6569380535082</v>
+        <v>423.8555749108771</v>
       </c>
       <c r="E98">
-        <v>1136.1844</v>
+        <v>1148.0383</v>
       </c>
       <c r="F98">
-        <v>1137.9744</v>
+        <v>1149.8283</v>
       </c>
       <c r="G98">
         <v>231.8</v>
@@ -9323,37 +9323,37 @@
         <v>126.8</v>
       </c>
       <c r="M98">
-        <v>228.50525952</v>
+        <v>230.88552264</v>
       </c>
       <c r="N98">
-        <v>-101.70525952</v>
+        <v>-104.08552264</v>
       </c>
       <c r="O98">
-        <v>-15.255788928</v>
+        <v>-15.612828396</v>
       </c>
       <c r="P98">
-        <v>-86.44947059199998</v>
+        <v>-88.47269424399998</v>
       </c>
       <c r="Q98">
-        <v>-75.54947059199999</v>
+        <v>-77.57269424399999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9573471662283459</v>
+        <v>1.261196221637795</v>
       </c>
       <c r="T98">
-        <v>17.29171290583467</v>
+        <v>23.05561720777957</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08323659612891872</v>
+        <v>0.08237848689047626</v>
       </c>
       <c r="W98">
-        <v>0.1840860914973131</v>
+        <v>0.1842583998323924</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5549106408594582</v>
+        <v>0.5491899126031752</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2165665344865545</v>
+        <v>0.2181165344865545</v>
       </c>
       <c r="C99">
-        <v>-494.1727250891229</v>
+        <v>-508.7914415615182</v>
       </c>
       <c r="D99">
-        <v>423.8555749108771</v>
+        <v>421.0907584384817</v>
       </c>
       <c r="E99">
-        <v>1148.0383</v>
+        <v>1159.8922</v>
       </c>
       <c r="F99">
-        <v>1149.8283</v>
+        <v>1161.6822</v>
       </c>
       <c r="G99">
         <v>231.8</v>
@@ -9405,37 +9405,37 @@
         <v>126.8</v>
       </c>
       <c r="M99">
-        <v>230.88552264</v>
+        <v>233.26578576</v>
       </c>
       <c r="N99">
-        <v>-104.08552264</v>
+        <v>-106.46578576</v>
       </c>
       <c r="O99">
-        <v>-15.612828396</v>
+        <v>-15.969867864</v>
       </c>
       <c r="P99">
-        <v>-88.47269424399998</v>
+        <v>-90.49591789600001</v>
       </c>
       <c r="Q99">
-        <v>-77.57269424399999</v>
+        <v>-79.59591789600002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.261196221637795</v>
+        <v>1.868894332456692</v>
       </c>
       <c r="T99">
-        <v>23.05561720777957</v>
+        <v>34.58342581166934</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08237848689047626</v>
+        <v>0.0815378900854714</v>
       </c>
       <c r="W99">
-        <v>0.1842583998323924</v>
+        <v>0.1844271916708373</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5491899126031752</v>
+        <v>0.5435859339031426</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2181165344865545</v>
+        <v>0.2196665344865545</v>
       </c>
       <c r="C100">
-        <v>-508.7914415615182</v>
+        <v>-523.3743219122443</v>
       </c>
       <c r="D100">
-        <v>421.0907584384817</v>
+        <v>418.3617780877555</v>
       </c>
       <c r="E100">
-        <v>1159.8922</v>
+        <v>1171.7461</v>
       </c>
       <c r="F100">
-        <v>1161.6822</v>
+        <v>1173.5361</v>
       </c>
       <c r="G100">
         <v>231.8</v>
@@ -9487,37 +9487,37 @@
         <v>126.8</v>
       </c>
       <c r="M100">
-        <v>233.26578576</v>
+        <v>235.64604888</v>
       </c>
       <c r="N100">
-        <v>-106.46578576</v>
+        <v>-108.84604888</v>
       </c>
       <c r="O100">
-        <v>-15.969867864</v>
+        <v>-16.32690733199999</v>
       </c>
       <c r="P100">
-        <v>-90.49591789600001</v>
+        <v>-92.51914154799998</v>
       </c>
       <c r="Q100">
-        <v>-79.59591789600002</v>
+        <v>-81.61914154799999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.868894332456692</v>
+        <v>3.691988664913384</v>
       </c>
       <c r="T100">
-        <v>34.58342581166934</v>
+        <v>69.16685162333869</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.0815378900854714</v>
+        <v>0.080714275034103</v>
       </c>
       <c r="W100">
-        <v>0.1844271916708373</v>
+        <v>0.1845925735731521</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5435859339031426</v>
+        <v>0.5380951668940201</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2196665344865545</v>
-      </c>
-      <c r="C101">
-        <v>-523.3743219122443</v>
-      </c>
-      <c r="D101">
-        <v>418.3617780877555</v>
-      </c>
-      <c r="E101">
-        <v>1171.7461</v>
-      </c>
-      <c r="F101">
-        <v>1173.5361</v>
-      </c>
-      <c r="G101">
-        <v>231.8</v>
-      </c>
-      <c r="H101">
-        <v>1183.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>137.7</v>
-      </c>
-      <c r="K101">
-        <v>10.89999999999999</v>
-      </c>
-      <c r="L101">
-        <v>126.8</v>
-      </c>
-      <c r="M101">
-        <v>235.64604888</v>
-      </c>
-      <c r="N101">
-        <v>-108.84604888</v>
-      </c>
-      <c r="O101">
-        <v>-16.32690733199999</v>
-      </c>
-      <c r="P101">
-        <v>-92.51914154799998</v>
-      </c>
-      <c r="Q101">
-        <v>-81.61914154799999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.691988664913384</v>
-      </c>
-      <c r="T101">
-        <v>69.16685162333869</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.080714275034103</v>
-      </c>
-      <c r="W101">
-        <v>0.1845925735731521</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5380951668940201</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
